--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -59,6 +59,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="51" state="visible" r:id="rId51"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="52" state="visible" r:id="rId52"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatchProgress" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharAnswer" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharReading" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClusterSubgroup" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseReading" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexical-Readiness" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="60" state="visible" r:id="rId60"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -607,7 +614,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1527,6 +1534,125 @@
         </is>
       </c>
       <c r="C56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BatchProgress.ps1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Live progress monitor over run_batch -- resume/skip/crash-safeguard mechanism (#1756).</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CharAnswer.ps1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Stage 4 (char-answers) -- answer battery for one subgroup.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CharReading.ps1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Stage 3 (char-reading) -- corpus-wide subgroup reading.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ClusterSubgroup.ps1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Stage 2 (char-subgroup) -- group cluster strongs into subgroups.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Lexical-Readiness.ps1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lexical readiness check.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VerseMeta.ps1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Verse-level metadata operations.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VerseReading.ps1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Stage 1 (verse-reading) -- per-cluster lexical-observation pass.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1699,12 +1825,14 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -1758,17 +1886,22 @@
           <t>-Set</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>-Title</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>-Question</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -1800,12 +1933,17 @@
           <t>Propose: JSON of new values, e.g. {"value":"12"}</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Propose: a short human label for the proposal</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Propose: representative description shown to the researcher</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>resume a specific paused proposal</t>
         </is>
@@ -1817,8 +1955,8 @@
           <t>iba\app\ps\Config-Maintenance.ps1</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6&lt;&gt;"",$J$4&amp;" ","")</f>
+      <c r="B6" s="23">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6&lt;&gt;"",$K$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -6146,6 +6284,524 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BatchProgress.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Live progress monitor over run_batch -- resume/skip/crash-safeguard mechanism (#1756).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-FilterRunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-SelectorKey</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\BatchProgress.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CharAnswer.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Stage 4 (char-answers) -- answer the characteristic-grain question battery for one subgroup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-SubgroupCode</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\CharAnswer.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CharReading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Stage 3 (char-reading) -- read one subgroup's member strongs corpus-wide, synergising meaning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-SubgroupCode</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\CharReading.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClusterSubgroup.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Stage 2 (char-subgroup) -- group a cluster's member strongs into meaning-based subgroups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\ClusterSubgroup.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VerseReading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Stage 1 (verse-reading) -- per-cluster, pre-subgroup lexical-observation pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseReading.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lexical-Readiness.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Lexical readiness check (lexical.readiness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Lexical-Readiness.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6255,6 +6911,92 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VerseMeta.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Verse-level metadata operations (currently: SetStatus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-References</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-Status</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseMeta.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -66,6 +66,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseReading" sheetId="58" state="visible" r:id="rId58"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexical-Readiness" sheetId="59" state="visible" r:id="rId59"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="62" state="visible" r:id="rId62"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -614,7 +616,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1653,6 +1655,40 @@
         </is>
       </c>
       <c r="C63" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Purge-SoftDeletes.ps1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>App-wide soft-delete purge audit (report only -- no delete capability yet, escalation #1766).</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>Observation-Enhancer.ps1</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>Apply a researcher-confirmed rule (selector+update) to ib_observation; logs every change (escalation #1778).</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -7002,6 +7038,183 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Purge-SoftDeletes.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>App-wide soft-delete purge audit across both databases -- per-table soft-deleted counts plus a live-dependency safety check. Report only; no delete/purge capability exists in this build (escalation #1766).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba/app/ps/Purge-SoftDeletes.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Observation-Enhancer.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Apply a researcher-confirmed cfg_observation_enhancer_rule to ib_observation (selector + update, logged to ib_observation_enhancer_log). Rules are authored/confirmed via Config-Maintenance.ps1 -Step Propose against cfg_observation_enhancer_rule -- not a separate add/confirm command here (escalation #1778).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-RuleKey</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Preview | Apply</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>cfg_observation_enhancer_rule.rule_key to run</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>resume a specific run</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>print every config read</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>iba/app/ps/Observation-Enhancer.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -68,6 +68,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="60" state="visible" r:id="rId60"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="61" state="visible" r:id="rId61"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="63" state="visible" r:id="rId63"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -616,7 +617,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1689,6 +1690,23 @@
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>Session-Close.ps1</t>
+        </is>
+      </c>
+      <c r="B66" s="23" t="inlineStr">
+        <is>
+          <t>Session-close checks: escalation update coverage, governance/doc drift, BUILD.md coverage (escalation #1875). Use /session-close for the full detect+remediate+commit cycle.</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -7215,6 +7233,77 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Session-Close.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Session-close checks -- escalation update coverage, governance/config/doc drift signal, BUILD.md tracking-id coverage for the current session (escalation #1875). Read-only detection, never blocks; use /session-close for detection + remediation + commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Session-Close.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -69,6 +69,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="61" state="visible" r:id="rId61"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="62" state="visible" r:id="rId62"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="64" state="visible" r:id="rId64"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -617,7 +618,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1707,6 +1708,23 @@
         </is>
       </c>
       <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Narrative-Register.ps1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>The narrative claim register in iba.db: claims, the passages that tell them, weaves recorded, search, history, check, and the three published files (escalation #2110).</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -7304,6 +7322,452 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Narrative-Register.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>The narrative claim register in iba.db (escalation #2110): add/edit claims, link them to passages, record a weave, search, history, check, publish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-By</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Claim</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-ClaimRef</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-Text</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>-BeyondText</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>-Source</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>-Origin</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>-Verdict</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-Status</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-IRead</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-MainChapter</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-MainSection</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-Chapter</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-Section</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-Passage</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-Kind</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-Part</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-Heading</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-NewHeading</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-Ordinal</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-Level</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>-LastVersion</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-NewNumber</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-Title</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-State</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-CurrentFile</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>-CurrentVersion</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-ReadingOrder</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>-Inactive</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-Note</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-Verse</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-Escalation</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-Thread</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>-NotInNarrative</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>-ToldInMoreThanOne</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>AddClaim|Edit|Tell|Untell|Withdraw|EditNote|EditChapter|EditSection|Record|Find|History|Check|Export</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Claude|Researcher (write actions)</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>claim ref, e.g. C-412 or K-2</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>AddClaim: keep a given ref (original claims)</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>the claim in its own wording / Find: text search / EditNote: block text</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>what the claim adds to its sources</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>verse refs and kind: text, e.g. Rom 7:15-21; lexical: kaas (anger)</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>narrative|original essay</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Stands|Widened|Restated|Withdrawn|Held|Added|New|Removed|Corrected</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>current|withdrawn|held</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0|1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>e.g. 10.1</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>heading text</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>e.g. 10.1 or 2</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>heading text</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>the passage's opening words</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>in full|in part|pointer</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>which part of the claim the passage tells</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>EditNote: block heading</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>EditNote/EditSection: new heading</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>EditSection: 2-4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>EditSection: last chapter version</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>EditChapter: new chapter number</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>EditChapter: title</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>draft|draft + held|empty|deferred</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>EditChapter: file name</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>EditChapter: version</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>EditChapter: order in the book</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0|1</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Record: the weave update JSON</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>a remark kept on the change rows</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Find: a verse reference</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Find: escalation id</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Find: OT-nn</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Find: switch (x to set)</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Find: switch (x to set)</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Narrative-Register.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="23">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6="","",$L$4&amp;" "&amp;L6&amp;" ")&amp;IF(M6="","",$M$4&amp;" "&amp;M6&amp;" ")&amp;IF(N6="","",$N$4&amp;" "&amp;N6&amp;" ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" "&amp;P6&amp;" ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" "&amp;W6&amp;" ")&amp;IF(X6="","",$X$4&amp;" "&amp;X6&amp;" ")&amp;IF(Y6="","",$Y$4&amp;" "&amp;Y6&amp;" ")&amp;IF(Z6="","",$Z$4&amp;" "&amp;Z6&amp;" ")&amp;IF(AA6="","",$AA$4&amp;" '"&amp;AA6&amp;"' ")&amp;IF(AB6="","",$AB$4&amp;" '"&amp;AB6&amp;"' ")&amp;IF(AC6="","",$AC$4&amp;" '"&amp;AC6&amp;"' ")&amp;IF(AD6="","",$AD$4&amp;" "&amp;AD6&amp;" ")&amp;IF(AE6="","",$AE$4&amp;" "&amp;AE6&amp;" ")&amp;IF(AF6="","",$AF$4&amp;" "&amp;AF6&amp;" ")&amp;IF(AG6="","",$AG$4&amp;" '"&amp;AG6&amp;"' ")&amp;IF(AH6="","",$AH$4&amp;" '"&amp;AH6&amp;"' ")&amp;IF(AI6="","",$AI$4&amp;" '"&amp;AI6&amp;"' ")&amp;IF(AJ6="","",$AJ$4&amp;" "&amp;AJ6&amp;" ")&amp;IF(AK6="","",$AK$4&amp;" "&amp;AK6&amp;" ")&amp;IF(AL6&lt;&gt;"",$AL$4&amp;" ","")&amp;IF(AM6&lt;&gt;"",$AM$4&amp;" ","")&amp;IF(AN6&lt;&gt;"",$AN$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -70,6 +70,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="62" state="visible" r:id="rId62"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="63" state="visible" r:id="rId63"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="68" state="visible" r:id="rId68"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -79,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +134,13 @@
       <b val="1"/>
       <color rgb="FFC00000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -184,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -253,6 +264,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,7 +631,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1534,7 +1547,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Base-data spine integrity + discoverability check (verse/span/strong sync, meaning-parse completeness). Triggered from start-project.</t>
+          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1653,7 +1666,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Stage 1 (verse-reading) -- per-cluster lexical-observation pass.</t>
+          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1670,7 +1683,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>App-wide soft-delete purge audit (report only -- no delete capability yet, escalation #1766).</t>
+          <t>The soft-delete purge audit + execute + database retirement -- app-wide, both databases (escalation #1766/#1868/#1872/#1873). Standalone work package (chained=0 -- each action is an independent step you invoke separately, not a pipeline).</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1704,7 +1717,7 @@
       </c>
       <c r="B66" s="23" t="inlineStr">
         <is>
-          <t>Session-close checks: escalation update coverage, governance/doc drift, BUILD.md coverage (escalation #1875). Use /session-close for the full detect+remediate+commit cycle.</t>
+          <t>Session-close detection (escalation #1875; rebuilt #2173, SC1-SC14): session and window, spine (FATAL first), researcher's words recorded, open items in the register, analysis integrity, rule compliance evidence, session log, decisions' targets, BUIL</t>
         </is>
       </c>
       <c r="C66" s="23" t="inlineStr">
@@ -1721,10 +1734,78 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The narrative claim register in iba.db: claims, the passages that tell them, weaves recorded, search, history, check, and the three published files (escalation #2110).</t>
+          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every act</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Compliance.ps1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>RelationalReading.ps1</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry poi</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Run-Stage1Batch.ps1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1744,7 +1825,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1812,6 +1893,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -1826,7 +1909,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1883,6 +1966,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -1897,7 +1982,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2117,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
@@ -2046,7 +2133,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2103,6 +2190,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -2117,7 +2206,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2279,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -2204,7 +2295,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2261,6 +2352,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -2275,7 +2368,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2358,6 +2451,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -2372,7 +2467,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2465,6 +2560,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
@@ -2479,7 +2576,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2577,6 +2674,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
@@ -2591,7 +2690,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2684,6 +2783,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
@@ -2698,7 +2799,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2766,6 +2867,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -2780,7 +2883,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
@@ -2801,6 +2904,12 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -2815,7 +2924,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2903,6 +3012,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -2917,7 +3028,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3006,6 +3117,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -3020,7 +3133,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3128,6 +3241,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
@@ -3142,7 +3257,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3220,6 +3335,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -3234,7 +3351,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3302,6 +3419,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -3325,50 +3444,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Spine-Check.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Base-data spine integrity + discoverability check (verse/span/strong sync, meaning-parse completeness, FATAL if broken).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning-parse completeness check + its discoverability pass were REMOVED 2026-09-11 (escalation #1681/#1684/#1686) — they checked coverage against strong_meaning_parsed/strong_lsj_parsed/strong_mounce_parsed, which were retired/frozen on 2026-09-10 and are no longer maintained. See handlers/spine.py module docstring.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>iba\app\ps\Spine-Check.ps1</t>
         </is>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
@@ -3387,7 +3512,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3444,6 +3569,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -3458,7 +3585,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3515,6 +3642,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -3529,7 +3658,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3597,6 +3726,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -3611,7 +3742,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3678,6 +3809,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -3692,7 +3825,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3780,6 +3913,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -3794,7 +3929,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3887,6 +4022,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
@@ -3901,7 +4038,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3969,6 +4106,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -3983,7 +4122,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4060,6 +4199,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
@@ -4074,7 +4215,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4151,6 +4292,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
@@ -4165,7 +4308,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4233,6 +4376,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -4247,7 +4392,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4465,6 +4610,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:W2"/>
@@ -4479,7 +4626,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4552,6 +4699,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -4566,7 +4715,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4623,6 +4772,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -4637,7 +4788,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4710,6 +4861,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -4724,7 +4877,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4791,6 +4944,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -4805,7 +4960,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4862,6 +5017,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -4876,7 +5033,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4933,6 +5090,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -4947,7 +5106,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5004,6 +5163,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -5018,7 +5179,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5075,6 +5236,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -5089,7 +5252,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5146,6 +5309,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -5160,7 +5325,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5228,6 +5393,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -5242,7 +5409,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5299,6 +5466,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -5313,7 +5482,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5386,6 +5555,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -5863,7 +6034,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5940,6 +6111,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
@@ -5954,7 +6127,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6017,6 +6190,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -6031,7 +6206,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6098,6 +6273,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6112,7 +6289,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6174,6 +6351,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -6188,7 +6367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6210,6 +6389,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -6232,6 +6412,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
@@ -6243,6 +6424,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6254,7 +6437,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6348,6 +6531,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
@@ -6362,7 +6547,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6439,6 +6624,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6453,7 +6640,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6531,6 +6718,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6545,7 +6734,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6623,6 +6812,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6637,7 +6828,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6709,6 +6900,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6723,7 +6916,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6735,63 +6928,87 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>VerseReading.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Stage 1 (verse-reading) -- per-cluster, pre-subgroup lexical-observation pass.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (Lexical and Semantic Analysis) only. Standalone single-step entry point onto the `verse-lexical` work package's `lexical.meaning` step (ordinal 6) -- this step didn't have a PS entry point until now, found live building this (`cfg_behaviour_rule` `every-interactive-module-needs-ps-script`). Run `RelationalReading.ps1` (`lexical.relational`) next for the same cluster once this has covered its verses -- the relational family (M0.6.5/M0.6.6/D7.7.1/M0.7/M0.8.1) moved there, with a readiness gate requiring this step's own output first.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>-ClusterCode</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-VerseList</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>-Live</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-Force</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="D5" s="17" t="n"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>iba\app\ps\VerseReading.ps1</t>
         </is>
       </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -6809,7 +7026,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6866,6 +7083,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6880,7 +7099,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6980,6 +7199,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
@@ -6994,7 +7215,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7066,6 +7287,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -7080,7 +7303,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7089,54 +7312,82 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Purge-SoftDeletes.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>App-wide soft-delete purge audit across both databases -- per-table soft-deleted counts plus a live-dependency safety check. Report only; no delete/purge capability exists in this build (escalation #1766).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The soft-delete purge audit + execute + database retirement -- app-wide, both databases (escalation #1766/#1868/#1872/#1873). Standalone work package (chained=0 -- each action is an independent step you invoke separately, not a pipeline).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-Database</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba/app/ps/Purge-SoftDeletes.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Purge-SoftDeletes.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -7151,7 +7402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7246,6 +7497,8 @@
       <c r="E6" s="23" t="n"/>
       <c r="F6" s="23" t="n"/>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7266,50 +7519,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Session-Close.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Session-close checks -- escalation update coverage, governance/config/doc drift signal, BUILD.md tracking-id coverage for the current session (escalation #1875). Read-only detection, never blocks; use /session-close for detection + remediation + commit.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Session-close detection (escalation #1875; rebuilt #2173, SC1-SC14): session and window, spine (FATAL first), researcher's words recorded, open items in the register, analysis integrity, rule compliance evidence, session log, decisions' targets, BUILD.md coverage, publish flags.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>iba\app\ps\Session-Close.ps1</t>
         </is>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
@@ -7328,7 +7587,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7339,244 +7598,274 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>Narrative-Register.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>The narrative claim register in iba.db (escalation #2110): add/edit claims, link them to passages, record a weave, search, history, check, publish.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every action dispatches through run.py, work package narrative-register.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>-Action</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>-By</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>-Claim</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>-ClaimRef</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>-Text</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="25" t="inlineStr">
         <is>
           <t>-BeyondText</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t>-Source</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>-Origin</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t>-Verdict</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="25" t="inlineStr">
         <is>
           <t>-Status</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t>-IRead</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="25" t="inlineStr">
         <is>
           <t>-MainChapter</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t>-MainSection</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="25" t="inlineStr">
         <is>
           <t>-Chapter</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t>-Section</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="25" t="inlineStr">
         <is>
           <t>-Passage</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="25" t="inlineStr">
         <is>
           <t>-Kind</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T4" s="25" t="inlineStr">
         <is>
           <t>-Part</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="25" t="inlineStr">
         <is>
           <t>-Heading</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V4" s="25" t="inlineStr">
         <is>
           <t>-NewHeading</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W4" s="25" t="inlineStr">
         <is>
           <t>-Ordinal</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="25" t="inlineStr">
         <is>
           <t>-Level</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" s="25" t="inlineStr">
         <is>
           <t>-LastVersion</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" s="25" t="inlineStr">
         <is>
           <t>-NewNumber</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA4" s="25" t="inlineStr">
         <is>
           <t>-Title</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB4" s="25" t="inlineStr">
         <is>
           <t>-State</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC4" s="25" t="inlineStr">
         <is>
           <t>-CurrentFile</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" s="25" t="inlineStr">
         <is>
           <t>-CurrentVersion</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE4" s="25" t="inlineStr">
         <is>
           <t>-ReadingOrder</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF4" s="25" t="inlineStr">
         <is>
           <t>-Inactive</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG4" s="25" t="inlineStr">
+        <is>
+          <t>-Purpose</t>
+        </is>
+      </c>
+      <c r="AH4" s="25" t="inlineStr">
+        <is>
+          <t>-PurposeRef</t>
+        </is>
+      </c>
+      <c r="AI4" s="25" t="inlineStr">
+        <is>
+          <t>-After</t>
+        </is>
+      </c>
+      <c r="AJ4" s="25" t="inlineStr">
+        <is>
+          <t>-BuiltFrom</t>
+        </is>
+      </c>
+      <c r="AK4" s="25" t="inlineStr">
+        <is>
+          <t>-FileStem</t>
+        </is>
+      </c>
+      <c r="AL4" s="25" t="inlineStr">
         <is>
           <t>-File</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AM4" s="25" t="inlineStr">
         <is>
           <t>-Note</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AN4" s="25" t="inlineStr">
+        <is>
+          <t>-Against</t>
+        </is>
+      </c>
+      <c r="AO4" s="25" t="inlineStr">
         <is>
           <t>-Verse</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AP4" s="25" t="inlineStr">
         <is>
           <t>-Escalation</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AQ4" s="25" t="inlineStr">
         <is>
           <t>-Thread</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AR4" s="25" t="inlineStr">
         <is>
           <t>-NotInNarrative</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AS4" s="25" t="inlineStr">
         <is>
           <t>-ToldInMoreThanOne</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AT4" s="25" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>AddClaim|Edit|Tell|Untell|Withdraw|EditNote|EditChapter|EditSection|Record|Find|History|Check|Export</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Claude|Researcher (write actions)</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>claim ref, e.g. C-412 or K-2</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>AddClaim: keep a given ref (original claims)</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>the claim in its own wording / Find: text search / EditNote: block text</t>
         </is>
@@ -7586,12 +7875,12 @@
           <t>what the claim adds to its sources</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>verse refs and kind: text, e.g. Rom 7:15-21; lexical: kaas (anger)</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>narrative|original essay</t>
         </is>
@@ -7706,65 +7995,404 @@
           <t>0|1</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>Record: the weave update JSON</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>a remark kept on the change rows</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>Find: a verse reference</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>Find: escalation id</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>Find: OT-nn</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>Find: switch (x to set)</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>Find: switch (x to set)</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>iba\app\ps\Narrative-Register.ps1</t>
         </is>
       </c>
-      <c r="B6" s="23">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6="","",$L$4&amp;" "&amp;L6&amp;" ")&amp;IF(M6="","",$M$4&amp;" "&amp;M6&amp;" ")&amp;IF(N6="","",$N$4&amp;" "&amp;N6&amp;" ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" "&amp;P6&amp;" ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" "&amp;W6&amp;" ")&amp;IF(X6="","",$X$4&amp;" "&amp;X6&amp;" ")&amp;IF(Y6="","",$Y$4&amp;" "&amp;Y6&amp;" ")&amp;IF(Z6="","",$Z$4&amp;" "&amp;Z6&amp;" ")&amp;IF(AA6="","",$AA$4&amp;" '"&amp;AA6&amp;"' ")&amp;IF(AB6="","",$AB$4&amp;" '"&amp;AB6&amp;"' ")&amp;IF(AC6="","",$AC$4&amp;" '"&amp;AC6&amp;"' ")&amp;IF(AD6="","",$AD$4&amp;" "&amp;AD6&amp;" ")&amp;IF(AE6="","",$AE$4&amp;" "&amp;AE6&amp;" ")&amp;IF(AF6="","",$AF$4&amp;" "&amp;AF6&amp;" ")&amp;IF(AG6="","",$AG$4&amp;" '"&amp;AG6&amp;"' ")&amp;IF(AH6="","",$AH$4&amp;" '"&amp;AH6&amp;"' ")&amp;IF(AI6="","",$AI$4&amp;" '"&amp;AI6&amp;"' ")&amp;IF(AJ6="","",$AJ$4&amp;" "&amp;AJ6&amp;" ")&amp;IF(AK6="","",$AK$4&amp;" "&amp;AK6&amp;" ")&amp;IF(AL6&lt;&gt;"",$AL$4&amp;" ","")&amp;IF(AM6&lt;&gt;"",$AM$4&amp;" ","")&amp;IF(AN6&lt;&gt;"",$AN$4&amp;" ","")</f>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Y6="","",$Y$4&amp;" '"&amp;Y6&amp;"' ")&amp;IF(Z6="","",$Z$4&amp;" '"&amp;Z6&amp;"' ")&amp;IF(AA6="","",$AA$4&amp;" '"&amp;AA6&amp;"' ")&amp;IF(AB6="","",$AB$4&amp;" '"&amp;AB6&amp;"' ")&amp;IF(AC6="","",$AC$4&amp;" '"&amp;AC6&amp;"' ")&amp;IF(AD6="","",$AD$4&amp;" '"&amp;AD6&amp;"' ")&amp;IF(AE6="","",$AE$4&amp;" '"&amp;AE6&amp;"' ")&amp;IF(AF6="","",$AF$4&amp;" '"&amp;AF6&amp;"' ")&amp;IF(AG6="","",$AG$4&amp;" '"&amp;AG6&amp;"' ")&amp;IF(AH6="","",$AH$4&amp;" '"&amp;AH6&amp;"' ")&amp;IF(AI6="","",$AI$4&amp;" '"&amp;AI6&amp;"' ")&amp;IF(AJ6="","",$AJ$4&amp;" '"&amp;AJ6&amp;"' ")&amp;IF(AK6="","",$AK$4&amp;" '"&amp;AK6&amp;"' ")&amp;IF(AL6="","",$AL$4&amp;" '"&amp;AL6&amp;"' ")&amp;IF(AM6="","",$AM$4&amp;" '"&amp;AM6&amp;"' ")&amp;IF(AN6="","",$AN$4&amp;" '"&amp;AN6&amp;"' ")&amp;IF(AO6="","",$AO$4&amp;" '"&amp;AO6&amp;"' ")&amp;IF(AP6="","",$AP$4&amp;" '"&amp;AP6&amp;"' ")&amp;IF(AQ6="","",$AQ$4&amp;" '"&amp;AQ6&amp;"' ")&amp;IF(AR6&lt;&gt;"",$AR$4&amp;" ","")&amp;IF(AS6&lt;&gt;"",$AS$4&amp;" ","")&amp;IF(AT6&lt;&gt;"",$AT$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Compliance.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-Phase</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Compliance.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-DryRun</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Copy-NarrativeToLearning4Comfort.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>RelationalReading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry point onto the `verse-lexical` work package's `lexical.relational` step (ordinal 7), mirroring `VerseReading.ps1` (`lexical.meaning`, the word-level half) exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-VerseList</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-Force</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\RelationalReading.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Run-Stage1Batch.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation #1756's own monitor, read- only over `run_batch` -- `lexical.meaning` already writes there via `batchcontrol.py`, so no new monitoring mechanism was needed, only this orchestration layer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-ClusterCodes</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-MaxTotalCostUsd</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Run-Stage1Batch.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -7774,7 +8402,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7882,6 +8510,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:K2"/>
@@ -7896,7 +8526,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7953,6 +8583,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -7967,7 +8599,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8044,6 +8676,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -3435,7 +3435,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3498,6 +3498,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -6916,7 +6918,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7012,6 +7014,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -7510,7 +7514,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7573,6 +7577,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -7587,7 +7593,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AT8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8047,6 +8053,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
@@ -8061,7 +8069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8105,12 +8113,17 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
+          <t>-Mode</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
         </is>
@@ -8123,7 +8136,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -8208,7 +8221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8229,6 +8242,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -8299,6 +8313,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8310,7 +8326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8331,6 +8347,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -8391,6 +8408,8 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -9,71 +9,55 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behaviour" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book-Narrative" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BookNarrative-Generate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BookNarrative-Validate" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build-Passages" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate-Curate" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate-Quality" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter-Generate" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Assign" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Report" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config-Maintenance" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-Rebuild" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-Search" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-SizeProfile" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="create-iba-view-template" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="create-passage-view-and-export" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="passages-by-book-view-export" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debate-Run" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="export-iba-config-tables" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export-Tables" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FolderPurpose" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="generate-iba-db-schema-report" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicon-Parse" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spine-Check" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log-Retention" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Rebuild" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Search" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Word" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations-Ingest" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passage-Quality" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PassageDebate-Report" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PassageDebate-Sync" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PathAudit" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prose" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Backfill" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry-Report" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-Report" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-BibleRes" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeedCandidate-Report" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set-Candidates" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpanAnalysis-Report" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-Iba" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongMeaning-Report" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongVerse-Report" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseLexical" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseSpanMeaning-Report" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatchProgress" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharAnswer" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharReading" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClusterSubgroup" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseReading" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexical-Readiness" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build-Passages" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Assign" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Report" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config-Maintenance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-Search" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-SizeProfile" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debate-Run" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export-Tables" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FolderPurpose" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicon-Parse" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spine-Check" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log-Retention" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Rebuild" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Search" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Word" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations-Ingest" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passage-Quality" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PathAudit" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prose" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Backfill" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry-Report" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-Report" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-BibleRes" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpanAnalysis-Report" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-Iba" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongMeaning-Report" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongVerse-Report" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseLexical" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatchProgress" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharAnswer" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharReading" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClusterSubgroup" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseReading" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexical-Readiness" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -631,7 +615,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -709,46 +693,46 @@
     <row r="7" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>BookNarrative-Generate.ps1</t>
+          <t>Build-Passages.ps1</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Generate the book-narrative draft.</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>Build passage rows from a payload.</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>BookNarrative-Validate.ps1</t>
+          <t>Cluster-Assign.ps1</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Validate a book-narrative file.</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>Assign strongs to M-code clusters / validate assignment.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Build-Passages.ps1</t>
+          <t>Cluster-Report.ps1</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Build passage rows from a payload.</t>
+          <t>Cluster overview report.</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -760,80 +744,80 @@
     <row r="10" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Candidate-Curate.ps1</t>
+          <t>Config-Maintenance.ps1</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>Curate candidate_seed rows (tag/decide/split/delete).</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>THE sanctioned path for changing a cfg_* row.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>Candidate-Quality.ps1</t>
+          <t>ContentIndex-Search.ps1</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>candidate_seed quality-check report.</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>Query the content search index.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>Chapter-Generate.ps1</t>
+          <t>ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Generate a chapter-level output.</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>Size-profile the content index.</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Cluster-Assign.ps1</t>
+          <t>Debate-Run.ps1</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Assign strongs to M-code clusters / validate assignment.</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Cluster-Report.ps1</t>
+          <t>Escalation.ps1</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>Cluster overview report.</t>
+          <t>See the researcher's own model sheet, 'escalation actions worksheet.xlsx' -- not rebuilt here, this tab is a pointer only.</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -845,12 +829,12 @@
     <row r="15" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Config-Maintenance.ps1</t>
+          <t>Export-Tables.ps1</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>THE sanctioned path for changing a cfg_* row.</t>
+          <t>Export one or more cfg_*/data tables to CSV.</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -862,12 +846,12 @@
     <row r="16" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>ContentIndex-Rebuild.ps1</t>
+          <t>FolderPurpose.ps1</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>Rebuild the content search index.</t>
+          <t>The folder_purpose governance mechanism (Methods A-D).</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -879,12 +863,12 @@
     <row r="17" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>ContentIndex-Search.ps1</t>
+          <t>Lexicon-Parse.ps1</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Query the content search index.</t>
+          <t>Parse strong_lexicon / related-word data.</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -896,12 +880,12 @@
     <row r="18" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>ContentIndex-SizeProfile.ps1</t>
+          <t>Log-Retention.ps1</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Size-profile the content index.</t>
+          <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -913,80 +897,80 @@
     <row r="19" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>create-iba-view-template.ps1</t>
+          <t>Manifest-Rebuild.ps1</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>Create/replace a named SQLite view in iba.db.</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>Rebuild the file_manifest table.</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>create-passage-view-and-export.ps1</t>
+          <t>Manifest-Search.ps1</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Create vw_passage_verse_top10 and export it to CSV.</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>Search the file_manifest table.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>create-passages-by-book-view-and-export.ps1</t>
+          <t>New-Word.ps1</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>Create vw_passages_by_book (scoped to one book) and export it.</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>Debate-Run.ps1</t>
+          <t>Operations-Ingest.ps1</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Escalation.ps1</t>
+          <t>Passage-Quality.ps1</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>See the researcher's own model sheet, 'escalation actions worksheet.xlsx' -- not rebuilt here, this tab is a pointer only.</t>
+          <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -998,29 +982,29 @@
     <row r="24" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>export-iba-config-tables.ps1</t>
+          <t>PathAudit.ps1</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Export all cfg_* tables to CSV + an index report.</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>Scan for hardcoded paths that should be config-driven.</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>Export-Tables.ps1</t>
+          <t>Prose.ps1</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>Export one or more cfg_*/data tables to CSV.</t>
+          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -1032,12 +1016,12 @@
     <row r="26" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>FolderPurpose.ps1</t>
+          <t>Raw-Backfill.ps1</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>The folder_purpose governance mechanism (Methods A-D).</t>
+          <t>Backfill span/strong_verse from raw span data for a book.</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1049,29 +1033,29 @@
     <row r="27" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>generate-iba-db-schema-report.ps1</t>
+          <t>Registry-Report.ps1</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>Generate the full iba.db schema overview doc.</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>word_registry overview report.</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Lexicon-Parse.ps1</t>
+          <t>Reports.ps1</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>Parse strong_lexicon / related-word data.</t>
+          <t>Word/book validation and report bundle.</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -1083,12 +1067,12 @@
     <row r="29" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Log-Retention.ps1</t>
+          <t>SchemaOverview-Report.ps1</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>Apply log-retention rules (prune old logs).</t>
+          <t>Live iba.db schema overview report.</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -1098,17 +1082,17 @@
       </c>
     </row>
     <row r="30" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Manifest-Rebuild.ps1</t>
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>Rebuild the file_manifest table.</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
+          <t>Live bible_research.db schema overview report (merged against cfg_table/cfg_column, discrepancies flagged).</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1117,12 +1101,12 @@
     <row r="31" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>Manifest-Search.ps1</t>
+          <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>Search the file_manifest table.</t>
+          <t>span table analysis report.</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
@@ -1134,29 +1118,29 @@
     <row r="32" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>New-Word.ps1</t>
+          <t>Start-Iba.ps1</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>Session bootstrap -- run once per session before any IBA work.</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>Operations-Ingest.ps1</t>
+          <t>StrongMeaning-Report.ps1</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -1168,12 +1152,12 @@
     <row r="34" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>Passage-Quality.ps1</t>
+          <t>StrongVerse-Report.ps1</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>Quality-check passages, optionally scoped to a book.</t>
+          <t>Report a word's strong&lt;-&gt;verse coverage.</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -1185,46 +1169,46 @@
     <row r="35" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>PassageDebate-Report.ps1</t>
+          <t>VerseLexical.ps1</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>Report on passage/debate state for a book.</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>PassageDebate-Sync.ps1</t>
+          <t>WholeBookRead-Report.ps1</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Sync file-based debate output back into passage/phenomenon.</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+          <t>Whole-book-read report for a book.</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>PathAudit.ps1</t>
+          <t>WordRegistrySpan-Report.ps1</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>Scan for hardcoded paths that should be config-driven.</t>
+          <t>Report a word's span coverage against its registry entry.</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
@@ -1234,289 +1218,289 @@
       </c>
     </row>
     <row r="38" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>Prose.ps1</t>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Catalogue-Report.ps1</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
+          <t>Structural review of wa_obs_question_catalogue (bible_research.db) -- no findings/joins. Read-only.</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>Raw-Backfill.ps1</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Backfill span/strong_verse from raw span data for a book.</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Catalogue-Update.ps1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Validated partial UPDATE of one wa_obs_question_catalogue row by obs_id (source/last_modified/etc.). No history table.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>Registry-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>word_registry overview report.</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Spine-Check.ps1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>Reports.ps1</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>Word/book validation and report bundle.</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BatchProgress.ps1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Live progress monitor over run_batch -- resume/skip/crash-safeguard mechanism (#1756).</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>SchemaOverview-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>Live iba.db schema overview report.</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CharAnswer.ps1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stage 4 (char-answers) -- answer battery for one subgroup.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>SchemaOverview-BibleResearch-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>Live bible_research.db schema overview report (merged against cfg_table/cfg_column, discrepancies flagged).</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CharReading.ps1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Stage 3 (char-reading) -- corpus-wide subgroup reading.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>SeedCandidate-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>candidate_seed coverage report.</t>
-        </is>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ClusterSubgroup.ps1</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Stage 2 (char-subgroup) -- group cluster strongs into subgroups.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>Set-Candidates.ps1</t>
-        </is>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>Seed candidate_seed rows for a book.</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lexical-Readiness.ps1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lexical readiness check.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>SpanAnalysis-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>span table analysis report.</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VerseMeta.ps1</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Verse-level metadata operations.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A47" s="18" t="inlineStr">
-        <is>
-          <t>Start-Iba.ps1</t>
-        </is>
-      </c>
-      <c r="B47" s="19" t="inlineStr">
-        <is>
-          <t>Session bootstrap -- run once per session before any IBA work.</t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VerseReading.ps1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A48" s="18" t="inlineStr">
-        <is>
-          <t>StrongMeaning-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Purge-SoftDeletes.ps1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>The soft-delete purge audit + execute + database retirement -- app-wide, both databases (escalation #1766/#1868/#1872/#1873). Standalone work package (chained=0 -- each action is an independent step you invoke separately, not a pipeline).</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t>StrongVerse-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>Report a word's strong&lt;-&gt;verse coverage.</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>Observation-Enhancer.ps1</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Apply a researcher-confirmed rule (selector+update) to ib_observation; logs every change (escalation #1778).</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>VerseLexical.ps1</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>Session-Close.ps1</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Session-close detection (escalation #1875; rebuilt #2173, SC1-SC14): session and window, spine (FATAL first), researcher's words recorded, open items in the register, analysis integrity, rule compliance evidence, session log, decisions' targets, BUIL</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>VerseSpanMeaning-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Report verse-span-meaning coverage for a book.</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>RETIRED</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Narrative-Register.ps1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every act</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>WholeBookRead-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>Whole-book-read report for a book.</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Compliance.ps1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
-        <is>
-          <t>WordRegistrySpan-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>Report a word's span coverage against its registry entry.</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
-        <is>
-          <t>Catalogue-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>Structural review of wa_obs_question_catalogue (bible_research.db) -- no findings/joins. Read-only.</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RelationalReading.ps1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry poi</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1525,287 +1509,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Catalogue-Update.ps1</t>
+          <t>Run-Stage1Batch.ps1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Validated partial UPDATE of one wa_obs_question_catalogue row by obs_id (source/last_modified/etc.). No history table.</t>
+          <t xml:space="preserve">Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Spine-Check.ps1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>BatchProgress.ps1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Live progress monitor over run_batch -- resume/skip/crash-safeguard mechanism (#1756).</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>CharAnswer.ps1</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Stage 4 (char-answers) -- answer battery for one subgroup.</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>CharReading.ps1</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Stage 3 (char-reading) -- corpus-wide subgroup reading.</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>ClusterSubgroup.ps1</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Stage 2 (char-subgroup) -- group cluster strongs into subgroups.</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Lexical-Readiness.ps1</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lexical readiness check.</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>VerseMeta.ps1</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Verse-level metadata operations.</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>VerseReading.ps1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Purge-SoftDeletes.ps1</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>The soft-delete purge audit + execute + database retirement -- app-wide, both databases (escalation #1766/#1868/#1872/#1873). Standalone work package (chained=0 -- each action is an independent step you invoke separately, not a pipeline).</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="23" t="inlineStr">
-        <is>
-          <t>Observation-Enhancer.ps1</t>
-        </is>
-      </c>
-      <c r="B65" s="23" t="inlineStr">
-        <is>
-          <t>Apply a researcher-confirmed rule (selector+update) to ib_observation; logs every change (escalation #1778).</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="23" t="inlineStr">
-        <is>
-          <t>Session-Close.ps1</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="inlineStr">
-        <is>
-          <t>Session-close detection (escalation #1875; rebuilt #2173, SC1-SC14): session and window, spine (FATAL first), researcher's words recorded, open items in the register, analysis integrity, rule compliance evidence, session log, decisions' targets, BUIL</t>
-        </is>
-      </c>
-      <c r="C66" s="23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Narrative-Register.ps1</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every act</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Compliance.ps1</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>RelationalReading.ps1</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry poi</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Run-Stage1Batch.ps1</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation </t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1825,25 +1537,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cluster-Assign.ps1</t>
+          <t>Debate-Run.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Assign strongs to M-code clusters / validate assignment.</t>
+          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
         </is>
       </c>
     </row>
@@ -1861,43 +1573,66 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Chapters</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Range</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-BookLabel</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>-Step</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Assign|Validate</t>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>hib.set|passage.build|phenomenon.set|operation.set|closing.set</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>resume a specific run</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Cluster-Assign.ps1</t>
+          <t>iba\app\ps\Debate-Run.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1909,68 +1644,30 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="34" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" min="2" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster-Report.ps1</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Escalation.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Cluster overview report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Cluster-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>See the researcher's own 'escalation actions worksheet.xlsx' -- that sheet already covers this script in full (Raise/Update/AnswerRun/etc) and is the model this whole workbook is based on. Not duplicated here.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1982,27 +1679,26 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Config-Maintenance.ps1</t>
+          <t>Export-Tables.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>THE sanctioned path for changing a cfg_* row.</t>
+          <t>Export one or more cfg_*/data tables to CSV.</t>
         </is>
       </c>
     </row>
@@ -2020,7 +1716,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Step</t>
+          <t>-Out</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -2030,98 +1726,51 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-Op</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>-Where</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-Set</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>-Title</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>-Question</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Database</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Validate|Propose|Report</t>
+          <t>output directory override</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>Propose: the cfg_* table, e.g. cfg_setting</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>insert|update|delete</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>Propose: JSON row-identifier, e.g. {"key":"passage.review_over"}</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>Propose: JSON of new values, e.g. {"value":"12"}</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Propose: a short human label for the proposal</t>
-        </is>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Propose: representative description shown to the researcher</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>resume a specific paused proposal</t>
+          <t>one or more table names, comma-separated -- repeat flag manually if needed</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>registered project database (default: iba) -- e.g. bible_research</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Config-Maintenance.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="23">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6&lt;&gt;"",$K$4&amp;" ","")</f>
+          <t>iba\app\ps\Export-Tables.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2133,25 +1782,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ContentIndex-Rebuild.ps1</t>
+          <t>FolderPurpose.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Rebuild the content search index.</t>
+          <t>The folder_purpose governance mechanism (Methods A-D).</t>
         </is>
       </c>
     </row>
@@ -2169,32 +1818,81 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-FolderPath</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Type</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Status</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-UsageDescription</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>-TopLevelRoot</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Seed|CrossCheck|AutoAssess|Set|List|Show</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>project-root-relative path</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>archive|operations|results</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>authoritative|mixed|reallocate|stale|deleted</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\ContentIndex-Rebuild.ps1</t>
+          <t>iba\app\ps\FolderPurpose.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6&lt;&gt;"",$J$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2206,25 +1904,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ContentIndex-Search.ps1</t>
+          <t>Lexicon-Parse.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Query the content search index.</t>
+          <t>Parse strong_lexicon / related-word data.</t>
         </is>
       </c>
     </row>
@@ -2242,48 +1940,41 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Query</t>
+          <t>-Step</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Csv</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>output as CSV</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Parse|Related|Validate</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\ContentIndex-Search.ps1</t>
+          <t>iba\app\ps\Lexicon-Parse.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2295,7 +1986,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2304,56 +1995,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ContentIndex-SizeProfile.ps1</t>
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Spine-Check.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Size-profile the content index.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning-parse completeness check + its discoverability pass were REMOVED 2026-09-11 (escalation #1681/#1684/#1686) — they checked coverage against strong_meaning_parsed/strong_lsj_parsed/strong_mounce_parsed, which were retired/frozen on 2026-09-10 and are no longer maintained. See handlers/spine.py module docstring.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\ContentIndex-SizeProfile.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Spine-Check.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -2368,25 +2063,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>create-iba-view-template.ps1</t>
+          <t>Log-Retention.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Create/replace a named SQLite view in iba.db.</t>
+          <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
     </row>
@@ -2404,58 +2099,30 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-DbPath</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-ViewName</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Apply</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-ReplaceExisting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba/app/db/iba.db</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>default: vw_cfg_table_catalogue</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>actually create/replace the view</t>
-        </is>
-      </c>
-    </row>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\create-iba-view-template.ps1</t>
+          <t>iba\app\ps\Log-Retention.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2467,25 +2134,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>create-passage-view-and-export.ps1</t>
+          <t>Manifest-Rebuild.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Create vw_passage_verse_top10 and export it to CSV.</t>
+          <t>Rebuild the file_manifest table.</t>
         </is>
       </c>
     </row>
@@ -2503,68 +2170,30 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-DbPath</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-ViewName</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-OutDir</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-CsvFileName</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-DryRun</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba/app/db/iba.db</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>default: vw_passage_verse_top10</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba/app/config</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>default: vw_passage_verse_top10.csv</t>
-        </is>
-      </c>
-    </row>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\create-passage-view-and-export.ps1</t>
+          <t>iba\app\ps\Manifest-Rebuild.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2576,25 +2205,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>create-passages-by-book-view-and-export.ps1</t>
+          <t>Manifest-Search.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Create vw_passages_by_book (scoped to one book) and export it.</t>
+          <t>Search the file_manifest table.</t>
         </is>
       </c>
     </row>
@@ -2612,73 +2241,41 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-DbPath</t>
+          <t>-Query</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-ViewName</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-OutDir</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-CsvFileName</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-DryRun</t>
+          <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>default: iba/app/db/iba.db</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>default: vw_passages_by_book</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>default: Rom</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba/app/config/views</t>
+          <t>e.g. grace, or registry:68, or type:observations</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\create-passages-by-book-view-and-export.ps1</t>
+          <t>iba\app\ps\Manifest-Search.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2690,25 +2287,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Debate-Run.ps1</t>
+          <t>New-Word.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
+          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
         </is>
       </c>
     </row>
@@ -2726,68 +2323,61 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
+          <t>-Word</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Chapters</t>
+          <t>-Source</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-Range</t>
+          <t>-Fresh</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-Step</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>hib.set|passage.build|phenomenon.set|operation.set|closing.set</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>resume a specific run</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>the English word, e.g. compassion</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>why this word -- provenance note</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>ignore any partial prior run</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>print every config read</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Debate-Run.ps1</t>
+          <t>iba\app\ps\New-Word.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2799,7 +2389,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2867,8 +2457,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -2883,36 +2471,102 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="2" max="6"/>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Escalation.ps1</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Operations-Ingest.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>See the researcher's own 'escalation actions worksheet.xlsx' -- that sheet already covers this script in full (Raise/Update/AnswerRun/etc) and is the model this whole workbook is based on. Not duplicated here.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Chapters</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Range</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-PayloadPath</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>hib.set|phenomenon.set|operation.set|closing.set</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>path to the payload JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Operations-Ingest.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2924,25 +2578,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>export-iba-config-tables.ps1</t>
+          <t>Passage-Quality.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Export all cfg_* tables to CSV + an index report.</t>
+          <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
     </row>
@@ -2960,63 +2614,41 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-DbPath</t>
+          <t>-Book</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-OutDir</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-ReportFileName</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-TableLike</t>
+          <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>default: iba/app/db/iba.db</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba/app/config</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>default: cfg-table-csv-index.md</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>default: cfg_%</t>
+          <t>omit for all books</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\export-iba-config-tables.ps1</t>
+          <t>iba\app\ps\Passage-Quality.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3028,26 +2660,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Export-Tables.ps1</t>
+          <t>PathAudit.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Export one or more cfg_*/data tables to CSV.</t>
+          <t>Scan for hardcoded paths that should be config-driven.</t>
         </is>
       </c>
     </row>
@@ -3065,63 +2696,41 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Out</t>
+          <t>-Action</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Table</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-Database</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>output directory override</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>one or more table names, comma-separated -- repeat flag manually if needed</t>
-        </is>
-      </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>registered project database (default: iba) -- e.g. bible_research</t>
+          <t>Scan</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Export-Tables.ps1</t>
+          <t>iba\app\ps\PathAudit.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3133,25 +2742,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FolderPurpose.ps1</t>
+          <t>Prose.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>The folder_purpose governance mechanism (Methods A-D).</t>
+          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
         </is>
       </c>
     </row>
@@ -3169,40 +2778,105 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Action</t>
+          <t>-Step</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-FolderPath</t>
+          <t>-Book</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-Type</t>
+          <t>-Chapter</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>-TypeId</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-IncludeBody</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>-AlsoMarkdown</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>-AlsoDocx</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>-Query</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>-Limit</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>-Fts</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>-InputFile</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>-Author</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>-FlagCode</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>-Description</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>-Find</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>-Replace</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>-ProposalFile</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>-SectionIds</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
           <t>-Status</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-UsageDescription</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-TopLevelRoot</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>-Out</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -3211,41 +2885,84 @@
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Seed|CrossCheck|AutoAssess|Set|List|Show</t>
+          <t>Extract|Search|ExportChapter|ImportChapter|Flag|FlagFixPropose|FlagFixApply|SetStatus</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>project-root-relative path</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>archive|operations|results</t>
+          <t>Programme|Detail design|Findings|Essays</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>authoritative|mixed|reallocate|stale|deleted</t>
+          <t>prose_section_type.id</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t>Search: use FTS5</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>ImportChapter</t>
+        </is>
+      </c>
+      <c r="Q5" s="17" t="inlineStr">
+        <is>
+          <t>FlagFixPropose</t>
+        </is>
+      </c>
+      <c r="R5" s="17" t="inlineStr">
+        <is>
+          <t>FlagFixPropose</t>
+        </is>
+      </c>
+      <c r="S5" s="17" t="inlineStr">
+        <is>
+          <t>FlagFixApply</t>
+        </is>
+      </c>
+      <c r="T5" s="17" t="inlineStr">
+        <is>
+          <t>SetStatus</t>
+        </is>
+      </c>
+      <c r="U5" s="17" t="inlineStr">
+        <is>
+          <t>draft|in_review|approved|archived</t>
+        </is>
+      </c>
+      <c r="V5" s="17" t="inlineStr">
+        <is>
+          <t>override output path</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\FolderPurpose.ps1</t>
+          <t>iba\app\ps\Prose.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6&lt;&gt;"",$J$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" "&amp;U6&amp;" ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6&lt;&gt;"",$W$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3257,25 +2974,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>generate-iba-db-schema-report.ps1</t>
+          <t>Raw-Backfill.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Generate the full iba.db schema overview doc.</t>
+          <t>Backfill span/strong_verse from raw span data for a book.</t>
         </is>
       </c>
     </row>
@@ -3293,53 +3010,46 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-DbPath</t>
+          <t>-Book</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-OutDir</t>
+          <t>-Range</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-BaseName</t>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba/app/db/iba.db</t>
-        </is>
-      </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>default: docs</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>default: iba-db-schema-overview</t>
+          <t>e.g. 1-9 (chapters)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\generate-iba-db-schema-report.ps1</t>
+          <t>iba\app\ps\Raw-Backfill.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3351,25 +3061,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Lexicon-Parse.ps1</t>
+          <t>Registry-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Parse strong_lexicon / related-word data.</t>
+          <t>word_registry overview report.</t>
         </is>
       </c>
     </row>
@@ -3387,43 +3097,30 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Step</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Parse|Related|Validate</t>
-        </is>
-      </c>
-    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Lexicon-Parse.ps1</t>
+          <t>iba\app\ps\Registry-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3435,74 +3132,82 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Spine-Check.ps1</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Reports.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning-parse completeness check + its discoverability pass were REMOVED 2026-09-11 (escalation #1681/#1684/#1686) — they checked coverage against strong_meaning_parsed/strong_lsj_parsed/strong_mounce_parsed, which were retired/frozen on 2026-09-10 and are no longer maintained. See handlers/spine.py module docstring.</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Word/book validation and report bundle.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Word</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>ReportWord|ValidationWord|ValidationBook</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Spine-Check.ps1</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Reports.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3514,7 +3219,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3525,14 +3230,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Log-Retention.ps1</t>
+          <t>SchemaOverview-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Apply log-retention rules (prune old logs).</t>
+          <t>Live iba.db schema overview report.</t>
         </is>
       </c>
     </row>
@@ -3560,10 +3265,10 @@
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Log-Retention.ps1</t>
+          <t>iba\app\ps\SchemaOverview-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3571,8 +3276,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -3587,7 +3290,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3598,14 +3301,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Manifest-Rebuild.ps1</t>
+          <t>SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Rebuild the file_manifest table.</t>
+          <t>Live bible_research.db schema overview report -- merged against cfg_table/cfg_column, table+column level, discrepancies flagged.</t>
         </is>
       </c>
     </row>
@@ -3633,10 +3336,10 @@
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Manifest-Rebuild.ps1</t>
+          <t>iba\app\ps\SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3644,8 +3347,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -3660,25 +3361,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Manifest-Search.ps1</t>
+          <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Search the file_manifest table.</t>
+          <t>span table analysis report.</t>
         </is>
       </c>
     </row>
@@ -3696,43 +3397,30 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Query</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>e.g. grace, or registry:68, or type:observations</t>
-        </is>
-      </c>
-    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Manifest-Search.ps1</t>
+          <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3744,7 +3432,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3811,8 +3499,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -3827,25 +3513,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>New-Word.ps1</t>
+          <t>Start-Iba.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
+          <t>Session bootstrap -- run once per session before any IBA work.</t>
         </is>
       </c>
     </row>
@@ -3863,63 +3549,41 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Word</t>
+          <t>-Reload</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Source</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Fresh</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
+          <t>-Reset</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>the English word, e.g. compassion</t>
+          <t>reseed config from source</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>why this word -- provenance note</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>ignore any partial prior run</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>print every config read</t>
+          <t>full reset</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\New-Word.ps1</t>
+          <t>iba\app\ps\Start-Iba.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3931,25 +3595,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Operations-Ingest.ps1</t>
+          <t>StrongMeaning-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
         </is>
       </c>
     </row>
@@ -3967,68 +3631,30 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Step</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-PayloadPath</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>hib.set|phenomenon.set|operation.set|closing.set</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>path to the payload JSON</t>
-        </is>
-      </c>
-    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Operations-Ingest.ps1</t>
+          <t>iba\app\ps\StrongMeaning-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4040,595 +3666,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Passage-Quality.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Quality-check passages, optionally scoped to a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>omit for all books</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Passage-Quality.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PassageDebate-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Report on passage/debate state for a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\PassageDebate-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PassageDebate-Sync.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Sync file-based debate output back into passage/phenomenon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\PassageDebate-Sync.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PathAudit.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Scan for hardcoded paths that should be config-driven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Action</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\PathAudit.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Prose.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Step</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapter</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-TypeId</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-IncludeBody</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-AlsoMarkdown</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>-AlsoDocx</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>-Query</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>-Limit</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>-Fts</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>-InputFile</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>-Author</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>-FlagCode</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>-Description</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>-Find</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>-Replace</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>-ProposalFile</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>-SectionIds</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>-Status</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>-Out</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Extract|Search|ExportChapter|ImportChapter|Flag|FlagFixPropose|FlagFixApply|SetStatus</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Programme|Detail design|Findings|Essays</t>
-        </is>
-      </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>prose_section_type.id</t>
-        </is>
-      </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="K5" s="17" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t>Search: use FTS5</t>
-        </is>
-      </c>
-      <c r="M5" s="17" t="inlineStr">
-        <is>
-          <t>ImportChapter</t>
-        </is>
-      </c>
-      <c r="Q5" s="17" t="inlineStr">
-        <is>
-          <t>FlagFixPropose</t>
-        </is>
-      </c>
-      <c r="R5" s="17" t="inlineStr">
-        <is>
-          <t>FlagFixPropose</t>
-        </is>
-      </c>
-      <c r="S5" s="17" t="inlineStr">
-        <is>
-          <t>FlagFixApply</t>
-        </is>
-      </c>
-      <c r="T5" s="17" t="inlineStr">
-        <is>
-          <t>SetStatus</t>
-        </is>
-      </c>
-      <c r="U5" s="17" t="inlineStr">
-        <is>
-          <t>draft|in_review|approved|archived</t>
-        </is>
-      </c>
-      <c r="V5" s="17" t="inlineStr">
-        <is>
-          <t>override output path</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Prose.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" "&amp;U6&amp;" ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6&lt;&gt;"",$W$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:W2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4639,14 +3677,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Raw-Backfill.ps1</t>
+          <t>StrongVerse-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Backfill span/strong_verse from raw span data for a book.</t>
+          <t>Report a word's strong&lt;-&gt;verse coverage.</t>
         </is>
       </c>
     </row>
@@ -4664,12 +3702,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
+          <t>-Word</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Range</t>
+          <t>-Strong</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4686,14 +3724,14 @@
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>e.g. 1-9 (chapters)</t>
+          <t>e.g. H2734</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Raw-Backfill.ps1</t>
+          <t>iba\app\ps\StrongVerse-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -4701,8 +3739,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -4711,863 +3747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Registry-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>word_registry overview report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Registry-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Reports.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Word/book validation and report bundle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Step</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Word</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>ReportWord|ValidationWord|ValidationBook</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Reports.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BookNarrative-Generate.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Generate the book-narrative draft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\BookNarrative-Generate.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SchemaOverview-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Live iba.db schema overview report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\SchemaOverview-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SchemaOverview-BibleResearch-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Live bible_research.db schema overview report -- merged against cfg_table/cfg_column, table+column level, discrepancies flagged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\SchemaOverview-BibleResearch-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SeedCandidate-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>candidate_seed coverage report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\SeedCandidate-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Set-Candidates.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Seed candidate_seed rows for a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Set-Candidates.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SpanAnalysis-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>span table analysis report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Start-Iba.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Session bootstrap -- run once per session before any IBA work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Reload</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>reseed config from source</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>full reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Start-Iba.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StrongMeaning-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\StrongMeaning-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StrongVerse-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Report a word's strong&lt;-&gt;verse coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Word</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Strong</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>e.g. H2734</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\StrongVerse-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -6030,185 +4210,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VerseSpanMeaning-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Report verse-span-meaning coverage for a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\VerseSpanMeaning-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BookNarrative-Validate.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Validate a book-narrative file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Path</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>path to the narrative file</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\BookNarrative-Validate.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6275,8 +4283,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6285,13 +4291,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6353,8 +4359,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
@@ -6363,13 +4367,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6391,7 +4395,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -6414,7 +4417,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
@@ -6426,20 +4428,18 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6533,8 +4533,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
@@ -6543,13 +4541,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6626,8 +4624,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6636,13 +4632,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6720,8 +4716,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6730,13 +4724,127 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
+    <col width="11.4" customWidth="1" min="8" max="8"/>
+    <col width="11.4" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Build-Passages.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Build passage rows from a payload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Chapters</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Range</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-PayloadPath</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>-Suggest</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>-Confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>path to the payload JSON</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>switch -- propose the next candidate passage boundary from cheap mechanical proxy signals (no table write, pauses for confirm/adjust); mutually exclusive with -Chapters/-Range</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>switch -- only with -Suggest: accept the suggestion verbatim, straight into passage.build (still needs -PayloadPath)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Build-Passages.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6814,8 +4922,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6824,13 +4930,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -6902,8 +5008,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -6912,13 +5016,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7014,8 +5118,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -7024,13 +5126,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7087,8 +5189,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -7097,129 +5197,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
-    <col width="11.4" customWidth="1" min="8" max="8"/>
-    <col width="11.4" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Build-Passages.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Build passage rows from a payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-PayloadPath</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>-Suggest</t>
-        </is>
-      </c>
-      <c r="I4" s="22" t="inlineStr">
-        <is>
-          <t>-Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>path to the payload JSON</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>switch -- propose the next candidate passage boundary from cheap mechanical proxy signals (no table write, pauses for confirm/adjust); mutually exclusive with -Chapters/-Range</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>switch -- only with -Suggest: accept the suggestion verbatim, straight into passage.build (still needs -PayloadPath)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Build-Passages.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7291,8 +5275,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
@@ -7301,13 +5283,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7390,8 +5372,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -7400,13 +5380,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7501,20 +5481,18 @@
       <c r="E6" s="23" t="n"/>
       <c r="F6" s="23" t="n"/>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -7577,8 +5555,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
@@ -7587,13 +5563,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT8"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -8053,8 +6029,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
@@ -8063,7 +6037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8145,13 +6119,95 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster-Assign.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Assign strongs to M-code clusters / validate assignment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Assign|Validate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Cluster-Assign.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8172,7 +6228,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -8208,20 +6263,18 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8242,7 +6295,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -8313,20 +6365,18 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8347,7 +6397,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -8408,10 +6457,79 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster-Report.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Cluster overview report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Cluster-Report.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8421,25 +6539,27 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="11"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="10"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Candidate-Curate.ps1</t>
+          <t>Config-Maintenance.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Curate candidate_seed rows (tag/decide/split/delete).</t>
+          <t>THE sanctioned path for changing a cfg_* row.</t>
         </is>
       </c>
     </row>
@@ -8457,32 +6577,32 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Mode</t>
+          <t>-Step</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-LemmaKey</t>
+          <t>-Table</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-Field</t>
+          <t>-Op</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>-StrongVariant</t>
+          <t>-Where</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-Value</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-InputFile</t>
+          <t>-Set</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>-Title</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -8504,36 +6624,59 @@
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Curate|Load</t>
+          <t>Validate|Propose|Report</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Propose: the cfg_* table, e.g. cfg_setting</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>tag|decision|split|delete</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>Load</t>
+          <t>insert|update|delete</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>Propose: JSON row-identifier, e.g. {"key":"passage.review_over"}</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Propose: JSON of new values, e.g. {"value":"12"}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Propose: a short human label for the proposal</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Propose: representative description shown to the researcher</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>resume a specific paused proposal</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Candidate-Curate.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
+          <t>iba\app\ps\Config-Maintenance.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="23">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6&lt;&gt;"",$K$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8545,25 +6688,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Candidate-Quality.ps1</t>
+          <t>ContentIndex-Search.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>candidate_seed quality-check report.</t>
+          <t>Query the content search index.</t>
         </is>
       </c>
     </row>
@@ -8581,32 +6724,46 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>-Query</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Csv</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>output as CSV</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Candidate-Quality.ps1</t>
+          <t>iba\app\ps\ContentIndex-Search.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8618,25 +6775,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="8"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chapter-Generate.ps1</t>
+          <t>ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Generate a chapter-level output.</t>
+          <t>Size-profile the content index.</t>
         </is>
       </c>
     </row>
@@ -8654,30 +6811,10 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -8687,19 +6824,17 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Chapter-Generate.ps1</t>
+          <t>iba\app\ps\ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -8,56 +8,54 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behaviour" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book-Narrative" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build-Passages" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Assign" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Report" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config-Maintenance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-Search" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-SizeProfile" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debate-Run" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export-Tables" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FolderPurpose" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicon-Parse" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spine-Check" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log-Retention" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Rebuild" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Search" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Word" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations-Ingest" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passage-Quality" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PathAudit" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prose" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Backfill" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry-Report" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-Report" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-BibleRes" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpanAnalysis-Report" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-Iba" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongMeaning-Report" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongVerse-Report" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseLexical" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordRegistrySpan-Report" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatchProgress" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharAnswer" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharReading" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClusterSubgroup" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseReading" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexical-Readiness" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build-Passages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Assign" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster-Report" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config-Maintenance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-Search" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ContentIndex-SizeProfile" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debate-Run" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escalation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export-Tables" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FolderPurpose" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexicon-Parse" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spine-Check" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log-Retention" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Rebuild" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manifest-Search" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Word" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operations-Ingest" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passage-Quality" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PathAudit" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prose" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw-Backfill" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry-Report" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reports" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-Report" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SchemaOverview-BibleRes" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpanAnalysis-Report" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start-Iba" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongMeaning-Report" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StrongVerse-Report" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseLexical" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WholeBookRead-Report" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Report" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogue-Update" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatchProgress" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharAnswer" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CharReading" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ClusterSubgroup" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseReading" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lexical-Readiness" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VerseMeta" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purge-SoftDeletes" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -615,7 +613,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -676,12 +674,12 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Book-Narrative.ps1</t>
+          <t>Build-Passages.ps1</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Run the book-narrative step for a book.</t>
+          <t>Build passage rows from a payload.</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -693,12 +691,12 @@
     <row r="7" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Build-Passages.ps1</t>
+          <t>Cluster-Assign.ps1</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>Build passage rows from a payload.</t>
+          <t>Assign strongs to M-code clusters / validate assignment.</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -710,12 +708,12 @@
     <row r="8" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Cluster-Assign.ps1</t>
+          <t>Cluster-Report.ps1</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>Assign strongs to M-code clusters / validate assignment.</t>
+          <t>Cluster overview report.</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -727,12 +725,12 @@
     <row r="9" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Cluster-Report.ps1</t>
+          <t>Config-Maintenance.ps1</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Cluster overview report.</t>
+          <t>THE sanctioned path for changing a cfg_* row.</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -744,12 +742,12 @@
     <row r="10" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Config-Maintenance.ps1</t>
+          <t>ContentIndex-Search.ps1</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>THE sanctioned path for changing a cfg_* row.</t>
+          <t>Query the content search index.</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -761,12 +759,12 @@
     <row r="11" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>ContentIndex-Search.ps1</t>
+          <t>ContentIndex-SizeProfile.ps1</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Query the content search index.</t>
+          <t>Size-profile the content index.</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -778,46 +776,46 @@
     <row r="12" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>ContentIndex-SizeProfile.ps1</t>
+          <t>Debate-Run.ps1</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>Size-profile the content index.</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>Debate-Run.ps1</t>
+          <t>Escalation.ps1</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>See the researcher's own model sheet, 'escalation actions worksheet.xlsx' -- not rebuilt here, this tab is a pointer only.</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Escalation.ps1</t>
+          <t>Export-Tables.ps1</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>See the researcher's own model sheet, 'escalation actions worksheet.xlsx' -- not rebuilt here, this tab is a pointer only.</t>
+          <t>Export one or more cfg_*/data tables to CSV.</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -829,12 +827,12 @@
     <row r="15" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Export-Tables.ps1</t>
+          <t>FolderPurpose.ps1</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>Export one or more cfg_*/data tables to CSV.</t>
+          <t>The folder_purpose governance mechanism (Methods A-D).</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -846,12 +844,12 @@
     <row r="16" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>FolderPurpose.ps1</t>
+          <t>Lexicon-Parse.ps1</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>The folder_purpose governance mechanism (Methods A-D).</t>
+          <t>Parse strong_lexicon / related-word data.</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -863,12 +861,12 @@
     <row r="17" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>Lexicon-Parse.ps1</t>
+          <t>Log-Retention.ps1</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>Parse strong_lexicon / related-word data.</t>
+          <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -880,12 +878,12 @@
     <row r="18" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>Log-Retention.ps1</t>
+          <t>Manifest-Rebuild.ps1</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
         <is>
-          <t>Apply log-retention rules (prune old logs).</t>
+          <t>Rebuild the file_manifest table.</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -897,12 +895,12 @@
     <row r="19" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Manifest-Rebuild.ps1</t>
+          <t>Manifest-Search.ps1</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>Rebuild the file_manifest table.</t>
+          <t>Search the file_manifest table.</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -914,12 +912,12 @@
     <row r="20" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>Manifest-Search.ps1</t>
+          <t>New-Word.ps1</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Search the file_manifest table.</t>
+          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -931,12 +929,12 @@
     <row r="21" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>New-Word.ps1</t>
+          <t>Operations-Ingest.ps1</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>Register a new word_registry entry and run its first-pass pipeline.</t>
+          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -948,12 +946,12 @@
     <row r="22" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>Operations-Ingest.ps1</t>
+          <t>Passage-Quality.ps1</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+          <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -965,12 +963,12 @@
     <row r="23" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Passage-Quality.ps1</t>
+          <t>PathAudit.ps1</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
-          <t>Quality-check passages, optionally scoped to a book.</t>
+          <t>Scan for hardcoded paths that should be config-driven.</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -982,12 +980,12 @@
     <row r="24" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>PathAudit.ps1</t>
+          <t>Prose.ps1</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>Scan for hardcoded paths that should be config-driven.</t>
+          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -999,12 +997,12 @@
     <row r="25" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>Prose.ps1</t>
+          <t>Raw-Backfill.ps1</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
+          <t>Backfill span/strong_verse from raw span data for a book.</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -1016,12 +1014,12 @@
     <row r="26" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>Raw-Backfill.ps1</t>
+          <t>Registry-Report.ps1</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>Backfill span/strong_verse from raw span data for a book.</t>
+          <t>word_registry overview report.</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -1033,12 +1031,12 @@
     <row r="27" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Registry-Report.ps1</t>
+          <t>Reports.ps1</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>word_registry overview report.</t>
+          <t>Word/book validation and report bundle.</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -1050,12 +1048,12 @@
     <row r="28" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Reports.ps1</t>
+          <t>SchemaOverview-Report.ps1</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>Word/book validation and report bundle.</t>
+          <t>Live iba.db schema overview report.</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -1065,34 +1063,34 @@
       </c>
     </row>
     <row r="29" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>SchemaOverview-Report.ps1</t>
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>Live iba.db schema overview report.</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
+          <t>Live bible_research.db schema overview report (merged against cfg_table/cfg_column, discrepancies flagged).</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>SchemaOverview-BibleResearch-Report.ps1</t>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
         <is>
-          <t>Live bible_research.db schema overview report (merged against cfg_table/cfg_column, discrepancies flagged).</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
+          <t>span table analysis report.</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1101,46 +1099,46 @@
     <row r="31" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>SpanAnalysis-Report.ps1</t>
+          <t>Start-Iba.ps1</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
         <is>
-          <t>span table analysis report.</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Active</t>
+          <t>Session bootstrap -- run once per session before any IBA work.</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>n/a (not dispatcher-gated)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>Start-Iba.ps1</t>
+          <t>StrongMeaning-Report.ps1</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
         <is>
-          <t>Session bootstrap -- run once per session before any IBA work.</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>n/a (not dispatcher-gated)</t>
+          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>StrongMeaning-Report.ps1</t>
+          <t>StrongVerse-Report.ps1</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
+          <t>Report a word's strong&lt;-&gt;verse coverage.</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -1152,12 +1150,12 @@
     <row r="34" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>StrongVerse-Report.ps1</t>
+          <t>VerseLexical.ps1</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>Report a word's strong&lt;-&gt;verse coverage.</t>
+          <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -1169,12 +1167,12 @@
     <row r="35" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>VerseLexical.ps1</t>
+          <t>WholeBookRead-Report.ps1</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>Run verse_lexical (L4b) derivation for a book/chapter range.</t>
+          <t>Whole-book-read report for a book.</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
@@ -1184,51 +1182,51 @@
       </c>
     </row>
     <row r="36" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>WholeBookRead-Report.ps1</t>
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>Catalogue-Report.ps1</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>Whole-book-read report for a book.</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
+          <t>Structural review of wa_obs_question_catalogue (bible_research.db) -- no findings/joins. Read-only.</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>WordRegistrySpan-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Report a word's span coverage against its registry entry.</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Catalogue-Update.ps1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Validated partial UPDATE of one wa_obs_question_catalogue row by obs_id (source/last_modified/etc.). No history table.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Catalogue-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>Structural review of wa_obs_question_catalogue (bible_research.db) -- no findings/joins. Read-only.</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Spine-Check.ps1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1237,12 +1235,12 @@
     <row r="39" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Catalogue-Update.ps1</t>
+          <t>BatchProgress.ps1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Validated partial UPDATE of one wa_obs_question_catalogue row by obs_id (source/last_modified/etc.). No history table.</t>
+          <t>Live progress monitor over run_batch -- resume/skip/crash-safeguard mechanism (#1756).</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1254,12 +1252,12 @@
     <row r="40" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Spine-Check.ps1</t>
+          <t>CharAnswer.ps1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning</t>
+          <t>Stage 4 (char-answers) -- answer battery for one subgroup.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1271,12 +1269,12 @@
     <row r="41" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BatchProgress.ps1</t>
+          <t>CharReading.ps1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Live progress monitor over run_batch -- resume/skip/crash-safeguard mechanism (#1756).</t>
+          <t>Stage 3 (char-reading) -- corpus-wide subgroup reading.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1288,12 +1286,12 @@
     <row r="42" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CharAnswer.ps1</t>
+          <t>ClusterSubgroup.ps1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stage 4 (char-answers) -- answer battery for one subgroup.</t>
+          <t>Stage 2 (char-subgroup) -- group cluster strongs into subgroups.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1305,12 +1303,12 @@
     <row r="43" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CharReading.ps1</t>
+          <t>Lexical-Readiness.ps1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stage 3 (char-reading) -- corpus-wide subgroup reading.</t>
+          <t>Lexical readiness check.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1322,12 +1320,12 @@
     <row r="44" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ClusterSubgroup.ps1</t>
+          <t>VerseMeta.ps1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Stage 2 (char-subgroup) -- group cluster strongs into subgroups.</t>
+          <t>Verse-level metadata operations.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1339,12 +1337,12 @@
     <row r="45" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lexical-Readiness.ps1</t>
+          <t>VerseReading.ps1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lexical readiness check.</t>
+          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1356,12 +1354,12 @@
     <row r="46" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VerseMeta.ps1</t>
+          <t>Purge-SoftDeletes.ps1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Verse-level metadata operations.</t>
+          <t>The soft-delete purge audit + execute + database retirement -- app-wide, both databases (escalation #1766/#1868/#1872/#1873). Standalone work package (chained=0 -- each action is an independent step you invoke separately, not a pipeline).</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1371,68 +1369,68 @@
       </c>
     </row>
     <row r="47" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>VerseReading.ps1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Observation-Enhancer.ps1</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Apply a researcher-confirmed rule (selector+update) to ib_observation; logs every change (escalation #1778).</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Purge-SoftDeletes.ps1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>The soft-delete purge audit + execute + database retirement -- app-wide, both databases (escalation #1766/#1868/#1872/#1873). Standalone work package (chained=0 -- each action is an independent step you invoke separately, not a pipeline).</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>Session-Close.ps1</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Session-close detection (escalation #1875; rebuilt #2173, SC1-SC14): session and window, spine (FATAL first), researcher's words recorded, open items in the register, analysis integrity, rule compliance evidence, session log, decisions' targets, BUIL</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>Observation-Enhancer.ps1</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Apply a researcher-confirmed rule (selector+update) to ib_observation; logs every change (escalation #1778).</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Narrative-Register.ps1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every act</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A50" s="23" t="inlineStr">
-        <is>
-          <t>Session-Close.ps1</t>
-        </is>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>Session-close detection (escalation #1875; rebuilt #2173, SC1-SC14): session and window, spine (FATAL first), researcher's words recorded, open items in the register, analysis integrity, rule compliance evidence, session log, decisions' targets, BUIL</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Compliance.ps1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1441,12 +1439,12 @@
     <row r="51" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Narrative-Register.ps1</t>
+          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every act</t>
+          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1458,12 +1456,12 @@
     <row r="52" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Compliance.ps1</t>
+          <t>RelationalReading.ps1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry poi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1475,49 +1473,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
+          <t>Run-Stage1Batch.ps1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
+          <t xml:space="preserve">Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>RelationalReading.ps1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry poi</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Run-Stage1Batch.ps1</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation </t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -1537,113 +1501,6 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Debate-Run.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-BookLabel</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-Step</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>hib.set|passage.build|phenomenon.set|operation.set|closing.set</t>
-        </is>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t>resume a specific run</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Debate-Run.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1673,7 +1530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -1776,7 +1633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -1898,7 +1755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -1975,6 +1832,83 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Spine-Check.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning-parse completeness check + its discoverability pass were REMOVED 2026-09-11 (escalation #1681/#1684/#1686) — they checked coverage against strong_meaning_parsed/strong_lsj_parsed/strong_mounce_parsed, which were retired/frozen on 2026-09-10 and are no longer maintained. See handlers/spine.py module docstring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Spine-Check.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1995,56 +1929,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Spine-Check.ps1</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Log-Retention.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The base-data spine check — verse/span/strong sync (FATAL per governance.base_data_spine, escalation #1613, researcher ruling 2026-09-10). Standalone, single-step work package, like Lexicon-Parse.ps1/Candidate-Quality.ps1. The strong-extended-meaning-parse completeness check + its discoverability pass were REMOVED 2026-09-11 (escalation #1681/#1684/#1686) — they checked coverage against strong_meaning_parsed/strong_lsj_parsed/strong_mounce_parsed, which were retired/frozen on 2026-09-10 and are no longer maintained. See handlers/spine.py module docstring.</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Apply log-retention rules (prune old logs).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18.75" customHeight="1"/>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>-RunId</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Spine-Check.ps1</t>
-        </is>
-      </c>
-      <c r="B6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Log-Retention.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
@@ -2074,14 +2002,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Log-Retention.ps1</t>
+          <t>Manifest-Rebuild.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Apply log-retention rules (prune old logs).</t>
+          <t>Rebuild the file_manifest table.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2040,7 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Log-Retention.ps1</t>
+          <t>iba\app\ps\Manifest-Rebuild.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -2129,77 +2057,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Manifest-Rebuild.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Rebuild the file_manifest table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Manifest-Rebuild.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -2281,7 +2138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -2378,6 +2235,113 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Operations-Ingest.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Chapters</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-Range</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-PayloadPath</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>hib.set|phenomenon.set|operation.set|closing.set</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>path to the payload JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Operations-Ingest.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2471,25 +2435,25 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Operations-Ingest.ps1</t>
+          <t>Passage-Quality.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Ingest a debate-step payload (hib/phenomenon/operation/closing).</t>
+          <t>Quality-check passages, optionally scoped to a book.</t>
         </is>
       </c>
     </row>
@@ -2507,35 +2471,15 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Step</t>
+          <t>-Book</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-PayloadPath</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -2544,29 +2488,24 @@
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>hib.set|phenomenon.set|operation.set|closing.set</t>
-        </is>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
-        <is>
-          <t>path to the payload JSON</t>
+          <t>omit for all books</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Operations-Ingest.ps1</t>
+          <t>iba\app\ps\Passage-Quality.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2589,14 +2528,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Passage-Quality.ps1</t>
+          <t>PathAudit.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Quality-check passages, optionally scoped to a book.</t>
+          <t>Scan for hardcoded paths that should be config-driven.</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2553,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Book</t>
+          <t>-Action</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -2631,18 +2570,18 @@
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>omit for all books</t>
+          <t>Scan</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Passage-Quality.ps1</t>
+          <t>iba\app\ps\PathAudit.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -2655,88 +2594,6 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PathAudit.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Scan for hardcoded paths that should be config-driven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Action</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\PathAudit.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -2968,7 +2825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3055,7 +2912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3126,7 +2983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3208,6 +3065,77 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SchemaOverview-Report.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Live iba.db schema overview report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\SchemaOverview-Report.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3230,14 +3158,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SchemaOverview-Report.ps1</t>
+          <t>SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Live iba.db schema overview report.</t>
+          <t>Live bible_research.db schema overview report -- merged against cfg_table/cfg_column, table+column level, discrepancies flagged.</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3196,7 @@
     <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\SchemaOverview-Report.ps1</t>
+          <t>iba\app\ps\SchemaOverview-BibleResearch-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3301,14 +3229,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SchemaOverview-BibleResearch-Report.ps1</t>
+          <t>SpanAnalysis-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Live bible_research.db schema overview report -- merged against cfg_table/cfg_column, table+column level, discrepancies flagged.</t>
+          <t>span table analysis report.</t>
         </is>
       </c>
     </row>
@@ -3336,10 +3264,10 @@
       </c>
     </row>
     <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="66.75" customFormat="1" customHeight="1" s="18">
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\SchemaOverview-BibleResearch-Report.ps1</t>
+          <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -3361,7 +3289,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3372,14 +3300,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SpanAnalysis-Report.ps1</t>
+          <t>Start-Iba.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>span table analysis report.</t>
+          <t>Session bootstrap -- run once per session before any IBA work.</t>
         </is>
       </c>
     </row>
@@ -3397,24 +3325,25 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+          <t>-Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>full reset</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\SpanAnalysis-Report.ps1</t>
+          <t>iba\app\ps\Start-Iba.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -3432,25 +3361,27 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
+    <col width="11.4" customWidth="1" min="8" max="8"/>
+    <col width="11.4" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Book-Narrative.ps1</t>
+          <t>Build-Passages.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Run the book-narrative step for a book.</t>
+          <t>Build passage rows from a payload.</t>
         </is>
       </c>
     </row>
@@ -3473,35 +3404,46 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-BookLabel</t>
+          <t>-Chapters</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>-RunId</t>
+          <t>-Range</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>-PayloadPath</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1"/>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>path to the payload JSON</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Book-Narrative.ps1</t>
+          <t>iba\app\ps\Build-Passages.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3524,14 +3466,14 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Start-Iba.ps1</t>
+          <t>StrongMeaning-Report.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Session bootstrap -- run once per session before any IBA work.</t>
+          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
         </is>
       </c>
     </row>
@@ -3549,35 +3491,24 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>-Reload</t>
+          <t>-RunId</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>-Reset</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>reseed config from source</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>full reset</t>
-        </is>
-      </c>
-    </row>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1"/>
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\Start-Iba.ps1</t>
+          <t>iba\app\ps\StrongMeaning-Report.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -3590,77 +3521,6 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StrongMeaning-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>strong_meaning_parsed/strong_lexicon coverage report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\StrongMeaning-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -3747,7 +3607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4210,7 +4070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4291,83 +4151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>WordRegistrySpan-Report.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Report a word's span coverage against its registry entry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Word</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1"/>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\WordRegistrySpan-Report.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4433,7 +4217,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4541,7 +4325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4632,7 +4416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4724,121 +4508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="7"/>
-    <col width="11.4" customWidth="1" min="8" max="8"/>
-    <col width="11.4" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Build-Passages.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Build passage rows from a payload.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Book</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-Chapters</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Range</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>-PayloadPath</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>-Suggest</t>
-        </is>
-      </c>
-      <c r="I4" s="22" t="inlineStr">
-        <is>
-          <t>-Confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t>path to the payload JSON</t>
-        </is>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>switch -- propose the next candidate passage boundary from cheap mechanical proxy signals (no table write, pauses for confirm/adjust); mutually exclusive with -Chapters/-Range</t>
-        </is>
-      </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>switch -- only with -Suggest: accept the suggestion verbatim, straight into passage.build (still needs -PayloadPath)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Build-Passages.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4919,6 +4589,284 @@
       </c>
       <c r="B6" s="5">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ClusterSubgroup.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Stage 2 (char-subgroup) -- group a cluster's member strongs into meaning-based subgroups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="D5" s="17" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\ClusterSubgroup.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cluster-Assign.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Assign strongs to M-code clusters / validate assignment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Assign|Validate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Cluster-Assign.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>VerseReading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (Lexical and Semantic Analysis) only. Standalone single-step entry point onto the `verse-lexical` work package's `lexical.meaning` step (ordinal 6) -- this step didn't have a PS entry point until now, found live building this (`cfg_behaviour_rule` `every-interactive-module-needs-ps-script`). Run `RelationalReading.ps1` (`lexical.relational`) next for the same cluster once this has covered its verses -- the relational family (M0.6.5/M0.6.6/D7.7.1/M0.7/M0.8.1) moved there, with a readiness gate requiring this step's own output first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-VerseList</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-Force</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\VerseReading.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -4942,22 +4890,19 @@
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ClusterSubgroup.ps1</t>
+          <t>Lexical-Readiness.ps1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Stage 2 (char-subgroup) -- group a cluster's member strongs into meaning-based subgroups.</t>
+          <t>Lexical readiness check (lexical.readiness).</t>
         </is>
       </c>
     </row>
@@ -4975,24 +4920,12 @@
       </c>
       <c r="C4" s="22" t="inlineStr">
         <is>
-          <t>-ClusterCode</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>-Live</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="D5" s="17" t="n"/>
@@ -5000,11 +4933,11 @@
     <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>iba\app\ps\ClusterSubgroup.ps1</t>
+          <t>iba\app\ps\Lexical-Readiness.ps1</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -5017,187 +4950,6 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>VerseReading.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The `verse-reading` stage's WORD-LEVEL half (`lexical.meaning`, escalation #1706 Phase C pipeline stage 1; narrowed to word-level-only by the #1860 split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.1 (Name and Naming) + M0.5 (Lexical and Semantic Analysis) only. Standalone single-step entry point onto the `verse-lexical` work package's `lexical.meaning` step (ordinal 6) -- this step didn't have a PS entry point until now, found live building this (`cfg_behaviour_rule` `every-interactive-module-needs-ps-script`). Run `RelationalReading.ps1` (`lexical.relational`) next for the same cluster once this has covered its verses -- the relational family (M0.6.5/M0.6.6/D7.7.1/M0.7/M0.8.1) moved there, with a readiness gate requiring this step's own output first.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>-ClusterCode</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>-VerseList</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>-Live</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>-Force</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>iba\app\ps\VerseReading.ps1</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lexical-Readiness.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Lexical readiness check (lexical.readiness).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="D5" s="17" t="n"/>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Lexical-Readiness.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -5283,7 +5035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -5380,7 +5132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5486,7 +5238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -5563,7 +5315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -6037,7 +5789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6119,89 +5871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="22" bestFit="1" customWidth="1" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster-Assign.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Assign strongs to M-code clusters / validate assignment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1"/>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>-Step</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>Assign|Validate</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Cluster-Assign.ps1</t>
-        </is>
-      </c>
-      <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6268,7 +5938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6370,99 +6040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Run-Stage1Batch.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation #1756's own monitor, read- only over `run_batch` -- `lexical.meaning` already writes there via `batchcontrol.py`, so no new monitoring mechanism was needed, only this orchestration layer).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>-ClusterCodes</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>-Live</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>-MaxTotalCostUsd</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>iba\app\ps\Run-Stage1Batch.ps1</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -6533,7 +6111,99 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Run-Stage1Batch.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Batch controller for `lexical.meaning` (Stage 1 verse-reading) -- runs an explicit list of clusters sequentially, unattended, so a multi-cluster pass can run in the background while progress is watched separately with `BatchProgress.ps1` (escalation #1756's own monitor, read- only over `run_batch` -- `lexical.meaning` already writes there via `batchcontrol.py`, so no new monitoring mechanism was needed, only this orchestration layer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-ClusterCodes</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-MaxTotalCostUsd</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Run-Stage1Batch.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -6682,7 +6352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -6769,7 +6439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -6838,4 +6508,111 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="60" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="22" bestFit="1" customWidth="1" min="3" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Debate-Run.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>The debate pipeline (HIB/phenomenon/operation/closing) for a book.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1"/>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>-Book</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>-Chapters</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>-Range</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>-BookLabel</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>hib.set|passage.build|phenomenon.set|operation.set|closing.set</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>resume a specific run</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customFormat="1" customHeight="1" s="18">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Debate-Run.ps1</t>
+        </is>
+      </c>
+      <c r="B6" s="5">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" "&amp;G6&amp;" ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -52,10 +52,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observation-Enhancer" sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strand-Reading" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -613,7 +614,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1410,7 +1411,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every act</t>
+          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the blocks that tell them, search, show a claim's history, check the chapters against the database, and publish the three register files. The narrative itself is written through Strand-Reading.ps1 -Step Rewrite (#2172). Every action dispatches through run.py, work package narrative-register.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1482,6 +1483,23 @@
         </is>
       </c>
       <c r="C53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Strand-Reading.ps1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>The reading process (escalation #2172): a strand defined, then context, record, gather, map, derive, rewrite and account. Every step dispatches through run.py, work package strand-reading; the JSON shapes are in lib/strandreading.py.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -3289,7 +3307,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -5341,7 +5359,7 @@
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the passages that tell them, record a weave, search, show a claim's history, check against the chapter files, and publish the three register files. Every action dispatches through run.py, work package narrative-register.</t>
+          <t>The narrative claim register in iba.db (escalation #2110): add and edit claims, link them to the blocks that tell them, search, show a claim's history, check the chapters against the database, and publish the three register files. The narrative itself is written through Strand-Reading.ps1 -Step Rewrite (#2172). Every action dispatches through run.py, work package narrative-register.</t>
         </is>
       </c>
     </row>
@@ -5434,154 +5452,150 @@
       </c>
       <c r="R4" s="25" t="inlineStr">
         <is>
-          <t>-Passage</t>
+          <t>-Kind</t>
         </is>
       </c>
       <c r="S4" s="25" t="inlineStr">
         <is>
-          <t>-Kind</t>
+          <t>-Part</t>
         </is>
       </c>
       <c r="T4" s="25" t="inlineStr">
         <is>
-          <t>-Part</t>
+          <t>-Heading</t>
         </is>
       </c>
       <c r="U4" s="25" t="inlineStr">
         <is>
-          <t>-Heading</t>
+          <t>-NewHeading</t>
         </is>
       </c>
       <c r="V4" s="25" t="inlineStr">
         <is>
-          <t>-NewHeading</t>
+          <t>-Ordinal</t>
         </is>
       </c>
       <c r="W4" s="25" t="inlineStr">
         <is>
-          <t>-Ordinal</t>
+          <t>-Level</t>
         </is>
       </c>
       <c r="X4" s="25" t="inlineStr">
         <is>
-          <t>-Level</t>
+          <t>-LastVersion</t>
         </is>
       </c>
       <c r="Y4" s="25" t="inlineStr">
         <is>
-          <t>-LastVersion</t>
+          <t>-NewNumber</t>
         </is>
       </c>
       <c r="Z4" s="25" t="inlineStr">
         <is>
-          <t>-NewNumber</t>
+          <t>-Title</t>
         </is>
       </c>
       <c r="AA4" s="25" t="inlineStr">
         <is>
-          <t>-Title</t>
+          <t>-State</t>
         </is>
       </c>
       <c r="AB4" s="25" t="inlineStr">
         <is>
-          <t>-State</t>
+          <t>-CurrentFile</t>
         </is>
       </c>
       <c r="AC4" s="25" t="inlineStr">
         <is>
-          <t>-CurrentFile</t>
+          <t>-CurrentVersion</t>
         </is>
       </c>
       <c r="AD4" s="25" t="inlineStr">
         <is>
-          <t>-CurrentVersion</t>
+          <t>-ReadingOrder</t>
         </is>
       </c>
       <c r="AE4" s="25" t="inlineStr">
         <is>
-          <t>-ReadingOrder</t>
+          <t>-Inactive</t>
         </is>
       </c>
       <c r="AF4" s="25" t="inlineStr">
         <is>
-          <t>-Inactive</t>
+          <t>-Purpose</t>
         </is>
       </c>
       <c r="AG4" s="25" t="inlineStr">
         <is>
-          <t>-Purpose</t>
+          <t>-PurposeRef</t>
         </is>
       </c>
       <c r="AH4" s="25" t="inlineStr">
         <is>
-          <t>-PurposeRef</t>
+          <t>-After</t>
         </is>
       </c>
       <c r="AI4" s="25" t="inlineStr">
         <is>
-          <t>-After</t>
+          <t>-BuiltFrom</t>
         </is>
       </c>
       <c r="AJ4" s="25" t="inlineStr">
         <is>
-          <t>-BuiltFrom</t>
+          <t>-FileStem</t>
         </is>
       </c>
       <c r="AK4" s="25" t="inlineStr">
         <is>
-          <t>-FileStem</t>
+          <t>-File</t>
         </is>
       </c>
       <c r="AL4" s="25" t="inlineStr">
         <is>
-          <t>-File</t>
+          <t>-Note</t>
         </is>
       </c>
       <c r="AM4" s="25" t="inlineStr">
         <is>
-          <t>-Note</t>
+          <t>-Against</t>
         </is>
       </c>
       <c r="AN4" s="25" t="inlineStr">
         <is>
-          <t>-Against</t>
+          <t>-Verse</t>
         </is>
       </c>
       <c r="AO4" s="25" t="inlineStr">
         <is>
-          <t>-Verse</t>
+          <t>-Escalation</t>
         </is>
       </c>
       <c r="AP4" s="25" t="inlineStr">
         <is>
-          <t>-Escalation</t>
+          <t>-Thread</t>
         </is>
       </c>
       <c r="AQ4" s="25" t="inlineStr">
         <is>
-          <t>-Thread</t>
+          <t>-NotInNarrative</t>
         </is>
       </c>
       <c r="AR4" s="25" t="inlineStr">
         <is>
-          <t>-NotInNarrative</t>
+          <t>-ToldInMoreThanOne</t>
         </is>
       </c>
       <c r="AS4" s="25" t="inlineStr">
         <is>
-          <t>-ToldInMoreThanOne</t>
-        </is>
-      </c>
-      <c r="AT4" s="25" t="inlineStr">
-        <is>
           <t>-Trace</t>
         </is>
       </c>
+      <c r="AT4" s="25" t="n"/>
     </row>
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" t="inlineStr">
         <is>
-          <t>AddClaim|Edit|Tell|Untell|Withdraw|EditNote|EditChapter|EditSection|Record|Find|History|Check|Export</t>
+          <t>AddClaim|Edit|Tell|Untell|Withdraw|EditNote|AddChapter|EditChapter|EditSection|Find|History|Check|Export|QuoteCheck</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5651,107 +5665,137 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>heading text</t>
+          <t>a block: its heading, or 'Parent &gt; Heading' where a heading repeats</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>the passage's opening words</t>
+          <t>in full|in part|pointer</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>in full|in part|pointer</t>
+          <t>which part of the claim the block tells</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>which part of the claim the passage tells</t>
+          <t>EditNote: block heading</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>EditNote: block heading</t>
+          <t>EditNote/EditSection: new heading</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>EditNote/EditSection: new heading</t>
+          <t>order</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>order</t>
+          <t>EditSection: 2-4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>EditSection: 2-4</t>
+          <t>EditSection: last chapter version</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>EditSection: last chapter version</t>
+          <t>EditChapter: new chapter number</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>EditChapter: new chapter number</t>
+          <t>EditChapter: title</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>EditChapter: title</t>
+          <t>draft|draft + held|empty|deferred</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>draft|draft + held|empty|deferred</t>
+          <t>EditChapter: file name</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>EditChapter: file name</t>
+          <t>EditChapter: version</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>EditChapter: version</t>
+          <t>EditChapter: order in the book</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>EditChapter: order in the book</t>
+          <t>0|1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0|1</t>
+          <t>AddChapter/EditChapter: what the chapter is for</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>the ruling, e.g. #2155</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>AddChapter/EditChapter: the chapter before</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>AddChapter</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>AddChapter</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>QuoteCheck: the chapter file</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Record: the weave update JSON</t>
+          <t>a remark kept on the change rows</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>a remark kept on the change rows</t>
+          <t>QuoteCheck: the previous version</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Find: a verse reference</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Find: a verse reference</t>
+          <t>Find: escalation id</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Find: escalation id</t>
+          <t>Find: OT-nn</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Find: OT-nn</t>
+          <t>Find: switch (x to set)</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -5760,11 +5804,6 @@
         </is>
       </c>
       <c r="AS5" t="inlineStr">
-        <is>
-          <t>Find: switch (x to set)</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
         </is>
@@ -5777,7 +5816,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Y6="","",$Y$4&amp;" '"&amp;Y6&amp;"' ")&amp;IF(Z6="","",$Z$4&amp;" '"&amp;Z6&amp;"' ")&amp;IF(AA6="","",$AA$4&amp;" '"&amp;AA6&amp;"' ")&amp;IF(AB6="","",$AB$4&amp;" '"&amp;AB6&amp;"' ")&amp;IF(AC6="","",$AC$4&amp;" '"&amp;AC6&amp;"' ")&amp;IF(AD6="","",$AD$4&amp;" '"&amp;AD6&amp;"' ")&amp;IF(AE6="","",$AE$4&amp;" '"&amp;AE6&amp;"' ")&amp;IF(AF6="","",$AF$4&amp;" '"&amp;AF6&amp;"' ")&amp;IF(AG6="","",$AG$4&amp;" '"&amp;AG6&amp;"' ")&amp;IF(AH6="","",$AH$4&amp;" '"&amp;AH6&amp;"' ")&amp;IF(AI6="","",$AI$4&amp;" '"&amp;AI6&amp;"' ")&amp;IF(AJ6="","",$AJ$4&amp;" '"&amp;AJ6&amp;"' ")&amp;IF(AK6="","",$AK$4&amp;" '"&amp;AK6&amp;"' ")&amp;IF(AL6="","",$AL$4&amp;" '"&amp;AL6&amp;"' ")&amp;IF(AM6="","",$AM$4&amp;" '"&amp;AM6&amp;"' ")&amp;IF(AN6="","",$AN$4&amp;" '"&amp;AN6&amp;"' ")&amp;IF(AO6="","",$AO$4&amp;" '"&amp;AO6&amp;"' ")&amp;IF(AP6="","",$AP$4&amp;" '"&amp;AP6&amp;"' ")&amp;IF(AQ6="","",$AQ$4&amp;" '"&amp;AQ6&amp;"' ")&amp;IF(AR6&lt;&gt;"",$AR$4&amp;" ","")&amp;IF(AS6&lt;&gt;"",$AS$4&amp;" ","")&amp;IF(AT6&lt;&gt;"",$AT$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Y6="","",$Y$4&amp;" '"&amp;Y6&amp;"' ")&amp;IF(Z6="","",$Z$4&amp;" '"&amp;Z6&amp;"' ")&amp;IF(AA6="","",$AA$4&amp;" '"&amp;AA6&amp;"' ")&amp;IF(AB6="","",$AB$4&amp;" '"&amp;AB6&amp;"' ")&amp;IF(AC6="","",$AC$4&amp;" '"&amp;AC6&amp;"' ")&amp;IF(AD6="","",$AD$4&amp;" '"&amp;AD6&amp;"' ")&amp;IF(AE6="","",$AE$4&amp;" '"&amp;AE6&amp;"' ")&amp;IF(AF6="","",$AF$4&amp;" '"&amp;AF6&amp;"' ")&amp;IF(AG6="","",$AG$4&amp;" '"&amp;AG6&amp;"' ")&amp;IF(AH6="","",$AH$4&amp;" '"&amp;AH6&amp;"' ")&amp;IF(AI6="","",$AI$4&amp;" '"&amp;AI6&amp;"' ")&amp;IF(AJ6="","",$AJ$4&amp;" '"&amp;AJ6&amp;"' ")&amp;IF(AK6="","",$AK$4&amp;" '"&amp;AK6&amp;"' ")&amp;IF(AL6="","",$AL$4&amp;" '"&amp;AL6&amp;"' ")&amp;IF(AM6="","",$AM$4&amp;" '"&amp;AM6&amp;"' ")&amp;IF(AN6="","",$AN$4&amp;" '"&amp;AN6&amp;"' ")&amp;IF(AO6="","",$AO$4&amp;" '"&amp;AO6&amp;"' ")&amp;IF(AP6="","",$AP$4&amp;" '"&amp;AP6&amp;"' ")&amp;IF(AQ6&lt;&gt;"",$AQ$4&amp;" ","")&amp;IF(AR6&lt;&gt;"",$AR$4&amp;" ","")&amp;IF(AS6&lt;&gt;"",$AS$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -5795,6 +5834,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Strand-Reading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The reading process (escalation #2172): a strand defined, then context, record, gather, map, derive, rewrite and account. Every step dispatches through run.py, work package strand-reading; the JSON shapes are in lib/strandreading.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Strand</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-By</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-Title</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Cluster</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-Escalation</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-Strongs</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-Note</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Define|Context|Record|Gather|Map|Derive|Rewrite|Account</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>the strand's code, e.g. flesh-body</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Claude|Researcher (Define, Context, Record, Map, Derive, Rewrite)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Define: the strand in words</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Define: home cluster, e.g. M48</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Define: the strand's escalation id</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Define: comma-separated exact codes, e.g. H1320,G4561</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Define: a note on the strand or its words</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Record/Map/Derive/Rewrite: the step's JSON</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Strand-Reading.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5871,7 +6064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5930,108 +6123,6 @@
       </c>
       <c r="B6">
         <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>RelationalReading.ps1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry point onto the `verse-lexical` work package's `lexical.relational` step (ordinal 7), mirroring `VerseReading.ps1` (`lexical.meaning`, the word-level half) exactly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>compiled command (copy/paste)</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>-ClusterCode</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>-VerseList</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>-Live</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>-Force</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>-RunId</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>-Trace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>switch (x to set)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>iba\app\ps\RelationalReading.ps1</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -6112,6 +6203,108 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>RelationalReading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The `verse-reading` stage's RELATIONAL half (`lexical.relational`, escalation #1860 word-level/ relational split, 2026-09-23) -- per-cluster, pre-subgroup Layer 2 pass answering M0.6.5/M0.6.6/ D7.7.1/M0.7.1-16/M0.8.1. Standalone single-step entry point onto the `verse-lexical` work package's `lexical.relational` step (ordinal 7), mirroring `VerseReading.ps1` (`lexical.meaning`, the word-level half) exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-ClusterCode</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-VerseList</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-Force</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>-RunId</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\RelationalReading.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -53,10 +53,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Session-Close" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Narrative-Register" sheetId="46" state="visible" r:id="rId46"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strand-Reading" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verse-Scope" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reading-Index" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verse-Collate" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open-Item" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reading" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compliance" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="56" state="visible" r:id="rId56"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -614,7 +619,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1500,6 +1505,91 @@
         </is>
       </c>
       <c r="C54" t="inlineStr">
+        <is>
+          <t>Retired 2026-10-23 (#2228 D-a): superseded by Reading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Verse-Scope.ps1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The scope resolver (escalation #2228): any request -&gt; the collection of verses as a JSON file under verse_scope.output_dir. Selectors are combined as a union; a bare Strong's code is decomposed to its derivatives; -OnlyStrong narrows the result. Reads only; dispatches through run.py, work package verse-scope.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Reading-Index.ps1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The cluster reading index (escalation #2228): Build reads the study files under reading_index.roots (only _analytics/Clusters) and records every verse reference with its file, section and line (reading_file, reading_section, reading_ref), incremental and time-guarded; Report writes the coverage report. Dispatches through run.py, work package reading-index.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Verse-Collate.ps1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>What is known and what is missing for a scope (escalation #2228): the scope resolved as Verse-Scope.ps1 does (same selectors, same guard), then per verse the observations, strand hits, claims, narrative blocks, open items and cluster-file lines, the lexicon per strong, and the gaps; -&gt; verse_collate.output_dir &lt;label&gt;.json and .md. Reads only; dispatches through run.py, work package verse-collate.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Open-Item.ps1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Register open items to a clear purpose (escalation #2236): Add, Reword, Split (a target scoped to verses, at most open_item.max_verses; what to read for, why it is open, when it comes back), Due (items that come back when a cluster is worked), Review (stragglers). Dispatches through run.py, work package open-item.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Reading.ps1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>The reading process (escalation #2228): a reading of one scope through three gates. Open (scope, collation, gap JSON), Record and Check (gate 1: every gap recorded or a reason; verses marked analysed), Synergy, Apply and Check (gate 2: from the tables -- claims, dispositions, tellings, blocks, open items settled), Publish (gate 3: chapters published and copied to learning4comfort), Account. Dispatches through run.py, work package reading.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -5847,11 +5937,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The reading process (escalation #2172): a strand defined, then context, record, gather, map, derive, rewrite and account. Every step dispatches through run.py, work package strand-reading; the JSON shapes are in lib/strandreading.py.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>RETIRED 2026-10-23 (#2228 D-a): superseded by Reading.ps1; the script is in iba/app/ps/archive/. The reading process (escalation #2172): a strand defined, then context, record, gather, map, derive, rewrite and account. Every step dispatches through run.py, work package strand-reading; the JSON shapes are in lib/strandreading.py.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -5969,7 +6058,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iba\app\ps\Strand-Reading.ps1</t>
+          <t>iba\app\ps\archive\Strand-Reading.ps1</t>
         </is>
       </c>
       <c r="B6">
@@ -5988,61 +6077,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Compliance.ps1</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Verse-Scope.ps1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+          <t>The scope resolver (escalation #2228): any request -&gt; the collection of verses as a JSON file under verse_scope.output_dir. Selectors are combined as a union; a bare Strong's code is decomposed to its derivatives; -OnlyStrong narrows the result. Reads only; dispatches through run.py, work package verse-scope.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>-Action</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="inlineStr">
-        <is>
-          <t>-Phase</t>
-        </is>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>-Mode</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Label</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Cluster</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-Subgroup</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-Strand</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Word</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-Strong</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-Verse</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-Chapter</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-Section</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-Claim</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-Observation</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-Item</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-Thread</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-OnlyStrong</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-Reviewed</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>names the output file(s), e.g. anger-bosom</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>e.g. M02 or M02,M01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>a cluster subgroup code</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>a strand code, e.g. anger</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>a word_registry word</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>e.g. H0430 (bare: all derivatives) or G3563G</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>e.g. Psa 10:2; Luk 14:12-14; Rom 8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>a narrative chapter, e.g. 10.1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>with -Chapter: a block heading</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>e.g. C-330</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>an ib_observation id</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>a thread item, e.g. OT-108.3</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>a thread, e.g. OT-108</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>a request JSON file (a batch or kept group)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>filter: keep verses holding one of these codes</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>over 2500 verses: the researcher's review, given after it</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
         </is>
@@ -6051,11 +6281,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iba\app\ps\Compliance.ps1</t>
+          <t>iba\app\ps\Verse-Scope.ps1</t>
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6&lt;&gt;"",$S$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -6070,47 +6300,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Reading-Index.ps1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
+          <t>The cluster reading index (escalation #2228): Build reads the study files under reading_index.roots (only _analytics/Clusters) and records every verse reference with its file, section and line (reading_file, reading_section, reading_ref), incremental and time-guarded; Report writes the coverage report. Dispatches through run.py, work package reading-index.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>script</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>compiled command (copy/paste)</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>-DryRun</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
+          <t>Build|Report</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>switch (x to set)</t>
         </is>
       </c>
@@ -6118,11 +6354,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>iba\app\ps\Copy-NarrativeToLearning4Comfort.ps1</t>
+          <t>iba\app\ps\Reading-Index.ps1</t>
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6&lt;&gt;"",$D$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -6208,6 +6444,864 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Verse-Collate.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is known and what is missing for a scope (escalation #2228): the scope resolved as Verse-Scope.ps1 does (same selectors, same guard), then per verse the observations, strand hits, claims, narrative blocks, open items and cluster-file lines, the lexicon per strong, and the gaps; -&gt; verse_collate.output_dir &lt;label&gt;.json and .md. Reads only; dispatches through run.py, work package verse-collate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Label</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Cluster</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-Subgroup</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-Strand</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Word</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-Strong</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-Verse</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-Chapter</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-Section</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-Claim</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-Observation</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-Item</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-Thread</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-OnlyStrong</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-Reviewed</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>names the output file(s), e.g. anger-bosom</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>e.g. M02 or M02,M01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>a cluster subgroup code</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>a strand code, e.g. anger</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>a word_registry word</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>e.g. H0430 (bare: all derivatives) or G3563G</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>e.g. Psa 10:2; Luk 14:12-14; Rom 8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>a narrative chapter, e.g. 10.1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>with -Chapter: a block heading</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>e.g. C-330</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>an ib_observation id</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>a thread item, e.g. OT-108.3</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>a thread, e.g. OT-108</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>a request JSON file (a batch or kept group)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>filter: keep verses holding one of these codes</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>over 2500 verses: the researcher's review, given after it</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Verse-Collate.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6&lt;&gt;"",$S$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Open-Item.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Register open items to a clear purpose (escalation #2236): Add, Reword, Split (a target scoped to verses, at most open_item.max_verses; what to read for, why it is open, when it comes back), Due (items that come back when a cluster is worked), Review (stragglers). Dispatches through run.py, work package open-item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Thread</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-Item</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-Origin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Anchor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-Source</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-TargetCluster</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-TargetTerms</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-Verse</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-ReadFor</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-Why</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-ComesBackWhen</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-Cluster</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-By</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Add|Reword|Split|Due|Review</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Add: OT-nn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reword/Split: OT-nn.n</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>the task/issue that raised it</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>strong:|verse:|observation:|claim:|block:</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>the source analysis's strong(s)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>e.g. M58</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>the related term(s) in the target cluster</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>or a verse target</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>what to read for</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>why it is open</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>the trigger</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>a JSON list of specs (Split: the parts)</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Due: the cluster being worked</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Claude|Researcher</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Open-Item.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" "&amp;Q6&amp;" ")&amp;IF(R6&lt;&gt;"",$R$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Reading.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The reading process (escalation #2228): a reading of one scope through three gates. Open (scope, collation, gap JSON), Record and Check (gate 1: every gap recorded or a reason; verses marked analysed), Synergy, Apply and Check (gate 2: from the tables -- claims, dispositions, tellings, blocks, open items settled), Publish (gate 3: chapters published and copied to learning4comfort), Account. Dispatches through run.py, work package reading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Label</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-By</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-Escalation</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Home</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-Note</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-Cluster</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-Subgroup</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-Strand</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-Word</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-Strong</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-Verse</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-Chapter</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-Section</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-Claim</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-Observation</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-Item</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>-Thread</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-OnlyStrong</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-Reviewed</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Open|Record|Check|Synergy|Apply|Publish|Account</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>the reading's name</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Claude|Researcher (write steps)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Open: the anchoring task/issue</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Open: the cluster new observations go under</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Open: a note</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Open: a scope request; Record: gap JSON; Apply: synergy JSON</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>scope filter</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>only after the researcher's review (&gt; 2,500 verses)</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Reading.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6&lt;&gt;"",$X$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Compliance.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The session compliance file (escalation #2173 P2): the governance settings, behaviour rules and escalation rules, restated at start and proved at close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-Action</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>-Phase</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>-Mode</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Compliance.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" "&amp;D6&amp;" ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Copy-NarrativeToLearning4Comfort.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Copy the current inner-being narrative files to the learning4comfort publication inbox (escalation #1941). This project never publishes to GitHub itself; the learning4comfort repo prepares, reviews and publishes from its inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>-DryRun</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Copy-NarrativeToLearning4Comfort.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6&lt;&gt;"",$C$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6304,7 +7398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -2707,7 +2707,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2725,7 +2725,7 @@
     <row r="2" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Prose store: extract/search/export/import/flag/status the programme prose.</t>
+          <t>Prose store: extract/search/export/import/flag/status the programme prose, and apply the reviewed patch.</t>
         </is>
       </c>
     </row>
@@ -2838,10 +2838,20 @@
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
+          <t>-PatchFile</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>-DryRun</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
           <t>-Out</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -2850,7 +2860,7 @@
     <row r="5" ht="18.75" customFormat="1" customHeight="1" s="18">
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>Extract|Search|ExportChapter|ImportChapter|Flag|FlagFixPropose|FlagFixApply|SetStatus</t>
+          <t>Extract|Search|ExportChapter|ImportChapter|Flag|FlagFixPropose|FlagFixApply|SetStatus|ApplyPatch</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -2909,6 +2919,16 @@
         </is>
       </c>
       <c r="V5" s="17" t="inlineStr">
+        <is>
+          <t>ApplyPatch: patch .json</t>
+        </is>
+      </c>
+      <c r="W5" s="17" t="inlineStr">
+        <is>
+          <t>ApplyPatch: roll back</t>
+        </is>
+      </c>
+      <c r="X5" s="17" t="inlineStr">
         <is>
           <t>override output path</t>
         </is>
@@ -2921,7 +2941,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" "&amp;U6&amp;" ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6&lt;&gt;"",$W$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" "&amp;F6&amp;" ")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")&amp;IF(H6&lt;&gt;"",$H$4&amp;" ","")&amp;IF(I6&lt;&gt;"",$I$4&amp;" ","")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" "&amp;K6&amp;" ")&amp;IF(L6&lt;&gt;"",$L$4&amp;" ","")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" "&amp;U6&amp;" ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6&lt;&gt;"",$W$4&amp;" ","")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Y6&lt;&gt;"",$Y$4&amp;" ","")</f>
         <v/>
       </c>
     </row>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-Home</t>
+          <t>-HomeCluster</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -6900,7 +6900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6913,7 +6913,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The reading process (escalation #2228): a reading of one scope through three gates. Open (scope, collation, gap JSON), Record and Check (gate 1: every gap recorded or a reason; verses marked analysed), Synergy, Apply and Check (gate 2: from the tables -- claims, dispositions, tellings, blocks, open items settled), Publish (gate 3: chapters published and copied to learning4comfort), Account. Dispatches through run.py, work package reading.</t>
+          <t>The reading process (escalations #2228, #2273): a reading of one scope with its objective, on the phases, through four gates. Open (0.C: scope, objective, collation, pre-gap JSON), Gather and Check (pre gate), Observe, Record and Check (observe gate: every word in focus, qualifiers included, has a finding of this reading, an open item or a reason; verses marked analysed), Synergy, Apply and Check (claims gate: every node disposed, every claim on a finding), Narrate and Check (narrate gate: every claim told or held), Publish, Account. Findings: one observation each, applied by nodes. Dispatches through run.py, work package reading.</t>
         </is>
       </c>
     </row>
@@ -6955,85 +6955,90 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-Objective</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-Note</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-File</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>-Cluster</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>-Subgroup</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>-Strand</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>-Word</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>-Strong</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>-Verse</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>-Chapter</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>-Section</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>-Claim</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>-Observation</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>-Item</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>-Thread</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>-OnlyStrong</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>-Reviewed</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -7042,7 +7047,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>Open|Record|Check|Synergy|Apply|Publish|Account</t>
+          <t>Open|Gather|Observe|Record|Check|Synergy|Apply|Narrate|Publish|Account</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7062,90 +7067,95 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Open: the cluster new observations go under</t>
+          <t>Open: the cluster the scope is anchored on (alias -Home)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Open: the scope's objective (0.C), in words</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Open: a note</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Open: a scope request; Record: gap JSON; Apply: synergy JSON</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>Open: a scope request; Gather: pre-gap JSON; Record: observe JSON; Apply: synergy JSON; Narrate: narrate JSON</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>scope filter</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>only after the researcher's review (&gt; 2,500 verses)</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
         </is>
@@ -7158,7 +7168,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6&lt;&gt;"",$X$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Y6&lt;&gt;"",$Y$4&amp;" ","")</f>
         <v/>
       </c>
     </row>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -62,6 +62,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy-NarrativeToLearning4Comfor" sheetId="54" state="visible" r:id="rId54"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="55" state="visible" r:id="rId55"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surface-Map" sheetId="57" state="visible" r:id="rId57"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -619,7 +620,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1590,6 +1591,23 @@
         </is>
       </c>
       <c r="C59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Surface-Map.ps1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>The surface mapping of an M cluster (escalation #2293, #2286 U3): Pairs writes the pairs file; Claude fills the groups and head; Apply writes it; Tail places the rest by the API (a preview unless -Live); Check reports group sizes, anomalies, unallocated and two-sense pairs. Dispatches through run.py, work package cluster-surface-map.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -7520,6 +7538,110 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Surface-Map.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The surface mapping of an M cluster (escalation #2293, #2286 U3): Pairs writes the pairs file; Claude fills the groups and head; Apply writes it; Tail places the rest by the API (a preview unless -Live); Check reports group sizes, anomalies, unallocated and two-sense pairs. Dispatches through run.py, work package cluster-surface-map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-Cluster</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-Live</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pairs | Apply | Tail | Check</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>an M cluster, e.g. M18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>with Apply: the filled pairs file</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>with Tail: switch (x to set): call the API; without it a preview</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Surface-Map.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -6115,8 +6115,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6128,10 +6132,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The scope resolver (escalation #2228): any request -&gt; the collection of verses as a JSON file under verse_scope.output_dir. Selectors are combined as a union; a bare Strong's code is decomposed to its derivatives; -OnlyStrong narrows the result. Reads only; dispatches through run.py, work package verse-scope.</t>
-        </is>
-      </c>
-    </row>
+          <t>The scope resolver (escalations #2228, #2295): any request -&gt; the collection of verses with their occurrences as a JSON file under verse_scope.output_dir. Selectors are combined as a union; a bare Strong's code is decomposed to its derivatives; a mapped M cluster or a subgroup enters through its (code, surface) pairs, a word through its surface; -HomeScope (alias -Home) names the home; -OnlyStrong narrows the result. Reads only; dispatches through run.py, work package verse-scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -6208,22 +6213,27 @@
           <t>-Thread</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="23" t="inlineStr">
+        <is>
+          <t>-HomeScope</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>-File</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>-OnlyStrong</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>-Reviewed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>-Trace</t>
         </is>
@@ -6295,22 +6305,27 @@
           <t>a thread, e.g. OT-108</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
+        <is>
+          <t>the home: a subgroup or an M cluster (alias -Home), when not the ones named</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>a request JSON file (a batch or kept group)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>filter: keep verses holding one of these codes</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>over 2500 verses: the researcher's review, given after it</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
         </is>
@@ -6323,7 +6338,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6&lt;&gt;"",$S$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6&lt;&gt;"",$T$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -7544,7 +7559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7561,7 +7576,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -63,6 +63,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RelationalReading" sheetId="55" state="visible" r:id="rId55"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-Stage1Batch" sheetId="56" state="visible" r:id="rId56"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surface-Map" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prior-Capture" sheetId="58" state="visible" r:id="rId58"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -620,7 +621,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1608,6 +1609,23 @@
         </is>
       </c>
       <c r="C60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Prior-Capture.ps1</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>The capture of prior study documents into the observation record (escalation #2305): Prepare writes the document's JSON (lines that name a verse, verses resolved, M/T-coded words, October ids); Claude fills findings and an answer per line; Record writes it whole or refuses it whole; Report shows where the capture stands. Dispatches through run.py, work package prior-capture.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -6136,7 +6154,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -7648,6 +7665,89 @@
       </c>
       <c r="B6">
         <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" '"&amp;E6&amp;"' ")&amp;IF(F6&lt;&gt;"",$F$4&amp;" ","")&amp;IF(G6&lt;&gt;"",$G$4&amp;" ","")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Prior-Capture.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The capture of prior study documents into the observation record (escalation #2305): Prepare writes the document's JSON (lines that name a verse, verses resolved, M/T-coded words, October ids); Claude fills findings and an answer per line; Record writes it whole or refuses it whole; Report shows where the capture stands. Dispatches through run.py, work package prior-capture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>compiled command (copy/paste)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-Step</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-File</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-Trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prepare | Record | Report</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>with Prepare: the document's repo-relative path or reading_file id; with Record: the filled JSON</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>switch (x to set)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>iba\app\ps\Prior-Capture.ps1</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" '"&amp;C6&amp;"' ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6&lt;&gt;"",$E$4&amp;" ","")</f>
         <v/>
       </c>
     </row>

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -6950,8 +6950,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6963,7 +6968,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The reading process (escalations #2228, #2273): a reading of one scope with its objective, on the phases, through four gates. Open (0.C: scope, objective, collation, pre-gap JSON), Gather and Check (pre gate), Observe, Record and Check (observe gate: every word in focus, qualifiers included, has a finding of this reading, an open item or a reason; verses marked analysed), Synergy, Apply and Check (claims gate: every node disposed, every claim on a finding), Narrate and Check (narrate gate: every claim told or held), Publish, Account. Findings: one observation each, applied by nodes. Dispatches through run.py, work package reading.</t>
+          <t>The reading process (escalations #2228, #2273, #2320). Analysis_phase_1 (the verse understanding): Open (0.C: ONE subgroup or a segment of it; the scope JSON that indexes the verses), Observe (the next verses in hand: each verse's sheet is read from the tables now), Record (the filled sheets: each surface evaluated, each existing observation and node accepted, modified or soft deleted, new findings written), Check (the Observe gate: every verse done; verses marked analysed). Gather is retired. Then Synergy, Apply and Check (claims gate), Narrate and Check (narrate gate), Publish, Account. Dispatches through run.py, work package reading.</t>
         </is>
       </c>
     </row>
@@ -7093,11 +7098,21 @@
           <t>-Trace</t>
         </is>
       </c>
+      <c r="Z4" s="23" t="inlineStr">
+        <is>
+          <t>-Surface</t>
+        </is>
+      </c>
+      <c r="AA4" s="23" t="inlineStr">
+        <is>
+          <t>-Count</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>Open|Gather|Observe|Record|Check|Synergy|Apply|Narrate|Publish|Account</t>
+          <t>Open|Observe|Record|Check|Synergy|Apply|Narrate|Publish|Account</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7117,7 +7132,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Open: the cluster the scope is anchored on (alias -Home)</t>
+          <t>not given for Open: the home is the subgroup's cluster (alias -Home)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7132,69 +7147,69 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Open: a scope request; Gather: pre-gap JSON; Record: observe JSON; Apply: synergy JSON; Narrate: narrate JSON</t>
+          <t>Apply: synergy JSON; Narrate: narrate JSON (Open takes no request file)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>not for Analysis_phase_1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Open: the ONE subgroup, which is the home</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Open: a segment (verses of the subgroup); Observe: the verse to put in hand</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>scope filter</t>
@@ -7208,6 +7223,16 @@
       <c r="Y5" t="inlineStr">
         <is>
           <t>switch (x to set)</t>
+        </is>
+      </c>
+      <c r="Z5" s="23" t="inlineStr">
+        <is>
+          <t>Open: a segment (surfaces of the subgroup, comma list)</t>
+        </is>
+      </c>
+      <c r="AA5" s="23" t="inlineStr">
+        <is>
+          <t>Observe: how many verses to put in hand (default reading.verse_loop)</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7243,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Y6&lt;&gt;"",$Y$4&amp;" ","")</f>
+        <f>A6&amp;" "&amp;IF(C6="","",$C$4&amp;" "&amp;C6&amp;" ")&amp;IF(D6="","",$D$4&amp;" '"&amp;D6&amp;"' ")&amp;IF(E6="","",$E$4&amp;" "&amp;E6&amp;" ")&amp;IF(F6="","",$F$4&amp;" '"&amp;F6&amp;"' ")&amp;IF(G6="","",$G$4&amp;" '"&amp;G6&amp;"' ")&amp;IF(H6="","",$H$4&amp;" '"&amp;H6&amp;"' ")&amp;IF(I6="","",$I$4&amp;" '"&amp;I6&amp;"' ")&amp;IF(J6="","",$J$4&amp;" '"&amp;J6&amp;"' ")&amp;IF(K6="","",$K$4&amp;" '"&amp;K6&amp;"' ")&amp;IF(L6="","",$L$4&amp;" '"&amp;L6&amp;"' ")&amp;IF(M6="","",$M$4&amp;" '"&amp;M6&amp;"' ")&amp;IF(N6="","",$N$4&amp;" '"&amp;N6&amp;"' ")&amp;IF(O6="","",$O$4&amp;" '"&amp;O6&amp;"' ")&amp;IF(P6="","",$P$4&amp;" '"&amp;P6&amp;"' ")&amp;IF(Q6="","",$Q$4&amp;" '"&amp;Q6&amp;"' ")&amp;IF(R6="","",$R$4&amp;" '"&amp;R6&amp;"' ")&amp;IF(S6="","",$S$4&amp;" '"&amp;S6&amp;"' ")&amp;IF(T6="","",$T$4&amp;" '"&amp;T6&amp;"' ")&amp;IF(U6="","",$U$4&amp;" '"&amp;U6&amp;"' ")&amp;IF(V6="","",$V$4&amp;" '"&amp;V6&amp;"' ")&amp;IF(W6="","",$W$4&amp;" '"&amp;W6&amp;"' ")&amp;IF(X6="","",$X$4&amp;" '"&amp;X6&amp;"' ")&amp;IF(Z6="","",$Z$4&amp;" '"&amp;Z6&amp;"' ")&amp;IF(AA6="","",$AA$4&amp;" '"&amp;AA6&amp;"' ")&amp;IF(Y6&lt;&gt;"",$Y$4&amp;" ","")</f>
         <v/>
       </c>
     </row>
@@ -7679,7 +7704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/iba/docs/ps tools worksheet.xlsx
+++ b/iba/docs/ps tools worksheet.xlsx
@@ -6972,6 +6972,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
